--- a/research/traditional_assets/database/data/south_africa/south_africa_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_chemical_basic.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1213783066963635</v>
+        <v>0.1210834352682833</v>
       </c>
       <c r="C2">
-        <v>49.6</v>
+        <v>49.24970558696599</v>
       </c>
       <c r="D2">
-        <v>37.2</v>
+        <v>37.345705586966</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.4960000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.4960000000000001</v>
       </c>
       <c r="G2">
         <v>12.4</v>
@@ -1451,28 +1451,28 @@
         <v>6.62</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0249488</v>
       </c>
       <c r="N2">
-        <v>6.62</v>
+        <v>6.5950512</v>
       </c>
       <c r="O2">
-        <v>1.7874</v>
+        <v>1.780663824</v>
       </c>
       <c r="P2">
-        <v>4.8326</v>
+        <v>4.814387376</v>
       </c>
       <c r="Q2">
-        <v>6.0026</v>
+        <v>5.984387376</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1213783066963635</v>
+        <v>0.1219356012810943</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470866</v>
+        <v>0.9120848850710198</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>265.3434233309819</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1210834352682833</v>
+        <v>0.1207885638402031</v>
       </c>
       <c r="C3">
-        <v>49.24970558696599</v>
+        <v>48.90055706638036</v>
       </c>
       <c r="D3">
-        <v>37.345705586966</v>
+        <v>37.49255706638036</v>
       </c>
       <c r="E3">
-        <v>0.4960000000000001</v>
+        <v>0.9920000000000001</v>
       </c>
       <c r="F3">
-        <v>0.4960000000000001</v>
+        <v>0.9920000000000001</v>
       </c>
       <c r="G3">
         <v>12.4</v>
@@ -1533,28 +1533,28 @@
         <v>6.62</v>
       </c>
       <c r="M3">
-        <v>0.0249488</v>
+        <v>0.0498976</v>
       </c>
       <c r="N3">
-        <v>6.5950512</v>
+        <v>6.5701024</v>
       </c>
       <c r="O3">
-        <v>1.780663824</v>
+        <v>1.773927648</v>
       </c>
       <c r="P3">
-        <v>4.814387376</v>
+        <v>4.796174752</v>
       </c>
       <c r="Q3">
-        <v>5.984387376</v>
+        <v>5.966174752</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1219356012810943</v>
+        <v>0.1225042692246971</v>
       </c>
       <c r="T3">
-        <v>0.9120848850710198</v>
+        <v>0.9188973805036045</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>265.3434233309819</v>
+        <v>132.6717116654909</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1207885638402031</v>
+        <v>0.1204936924121229</v>
       </c>
       <c r="C4">
-        <v>48.90055706638036</v>
+        <v>48.55256800930635</v>
       </c>
       <c r="D4">
-        <v>37.49255706638036</v>
+        <v>37.64056800930635</v>
       </c>
       <c r="E4">
-        <v>0.9920000000000001</v>
+        <v>1.488</v>
       </c>
       <c r="F4">
-        <v>0.9920000000000001</v>
+        <v>1.488</v>
       </c>
       <c r="G4">
         <v>12.4</v>
@@ -1615,28 +1615,28 @@
         <v>6.62</v>
       </c>
       <c r="M4">
-        <v>0.0498976</v>
+        <v>0.07484639999999999</v>
       </c>
       <c r="N4">
-        <v>6.5701024</v>
+        <v>6.5451536</v>
       </c>
       <c r="O4">
-        <v>1.773927648</v>
+        <v>1.767191472</v>
       </c>
       <c r="P4">
-        <v>4.796174752</v>
+        <v>4.777962128</v>
       </c>
       <c r="Q4">
-        <v>5.966174752</v>
+        <v>5.947962127999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1225042692246971</v>
+        <v>0.1230846622805391</v>
       </c>
       <c r="T4">
-        <v>0.9188973805036045</v>
+        <v>0.9258503397595415</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>132.6717116654909</v>
+        <v>88.44780777699395</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1204936924121229</v>
+        <v>0.1201988209840428</v>
       </c>
       <c r="C5">
-        <v>48.55256800930635</v>
+        <v>48.20575220195683</v>
       </c>
       <c r="D5">
-        <v>37.64056800930635</v>
+        <v>37.78975220195683</v>
       </c>
       <c r="E5">
-        <v>1.488</v>
+        <v>1.984</v>
       </c>
       <c r="F5">
-        <v>1.488</v>
+        <v>1.984</v>
       </c>
       <c r="G5">
         <v>12.4</v>
@@ -1697,28 +1697,28 @@
         <v>6.62</v>
       </c>
       <c r="M5">
-        <v>0.07484639999999999</v>
+        <v>0.0997952</v>
       </c>
       <c r="N5">
-        <v>6.5451536</v>
+        <v>6.5202048</v>
       </c>
       <c r="O5">
-        <v>1.767191472</v>
+        <v>1.760455296</v>
       </c>
       <c r="P5">
-        <v>4.777962128</v>
+        <v>4.759749504</v>
       </c>
       <c r="Q5">
-        <v>5.947962127999999</v>
+        <v>5.929749504</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1230846622805391</v>
+        <v>0.1236771468583779</v>
       </c>
       <c r="T5">
-        <v>0.9258503397595415</v>
+        <v>0.9329481523333106</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>88.44780777699395</v>
+        <v>66.33585583274547</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1201988209840428</v>
+        <v>0.1199039495559626</v>
       </c>
       <c r="C6">
-        <v>48.20575220195683</v>
+        <v>47.86012364997489</v>
       </c>
       <c r="D6">
-        <v>37.78975220195683</v>
+        <v>37.94012364997489</v>
       </c>
       <c r="E6">
-        <v>1.984</v>
+        <v>2.48</v>
       </c>
       <c r="F6">
-        <v>1.984</v>
+        <v>2.48</v>
       </c>
       <c r="G6">
         <v>12.4</v>
@@ -1779,28 +1779,28 @@
         <v>6.62</v>
       </c>
       <c r="M6">
-        <v>0.0997952</v>
+        <v>0.124744</v>
       </c>
       <c r="N6">
-        <v>6.5202048</v>
+        <v>6.495256</v>
       </c>
       <c r="O6">
-        <v>1.760455296</v>
+        <v>1.75371912</v>
       </c>
       <c r="P6">
-        <v>4.759749504</v>
+        <v>4.74153688</v>
       </c>
       <c r="Q6">
-        <v>5.929749504</v>
+        <v>5.91153688</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1236771468583779</v>
+        <v>0.1242821047957501</v>
       </c>
       <c r="T6">
-        <v>0.9329481523333106</v>
+        <v>0.9401953925402114</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>66.33585583274547</v>
+        <v>53.06868466619636</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1199039495559626</v>
+        <v>0.1196090781278824</v>
       </c>
       <c r="C7">
-        <v>47.86012364997489</v>
+        <v>47.51569658281689</v>
       </c>
       <c r="D7">
-        <v>37.94012364997489</v>
+        <v>38.09169658281689</v>
       </c>
       <c r="E7">
-        <v>2.48</v>
+        <v>2.976</v>
       </c>
       <c r="F7">
-        <v>2.48</v>
+        <v>2.976</v>
       </c>
       <c r="G7">
         <v>12.4</v>
@@ -1861,28 +1861,28 @@
         <v>6.62</v>
       </c>
       <c r="M7">
-        <v>0.124744</v>
+        <v>0.1496928</v>
       </c>
       <c r="N7">
-        <v>6.495256</v>
+        <v>6.4703072</v>
       </c>
       <c r="O7">
-        <v>1.75371912</v>
+        <v>1.746982944</v>
       </c>
       <c r="P7">
-        <v>4.74153688</v>
+        <v>4.723324256</v>
       </c>
       <c r="Q7">
-        <v>5.91153688</v>
+        <v>5.893324256</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1242821047957501</v>
+        <v>0.1248999341785983</v>
       </c>
       <c r="T7">
-        <v>0.9401953925402114</v>
+        <v>0.9475968293472594</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>53.06868466619636</v>
+        <v>44.22390388849697</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1196090781278824</v>
+        <v>0.1193142066998022</v>
       </c>
       <c r="C8">
-        <v>47.51569658281689</v>
+        <v>47.17248545824117</v>
       </c>
       <c r="D8">
-        <v>38.09169658281689</v>
+        <v>38.24448545824117</v>
       </c>
       <c r="E8">
-        <v>2.976</v>
+        <v>3.472</v>
       </c>
       <c r="F8">
-        <v>2.976</v>
+        <v>3.472</v>
       </c>
       <c r="G8">
         <v>12.4</v>
@@ -1943,28 +1943,28 @@
         <v>6.62</v>
       </c>
       <c r="M8">
-        <v>0.1496928</v>
+        <v>0.1746416</v>
       </c>
       <c r="N8">
-        <v>6.4703072</v>
+        <v>6.4453584</v>
       </c>
       <c r="O8">
-        <v>1.746982944</v>
+        <v>1.740246768</v>
       </c>
       <c r="P8">
-        <v>4.723324256</v>
+        <v>4.705111631999999</v>
       </c>
       <c r="Q8">
-        <v>5.893324256</v>
+        <v>5.875111631999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1248999341785983</v>
+        <v>0.1255310502148411</v>
       </c>
       <c r="T8">
-        <v>0.9475968293472594</v>
+        <v>0.9551574368383298</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>44.22390388849698</v>
+        <v>37.90620333299741</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1193142066998022</v>
+        <v>0.119019335271722</v>
       </c>
       <c r="C9">
-        <v>47.17248545824118</v>
+        <v>46.83050496690529</v>
       </c>
       <c r="D9">
-        <v>38.24448545824118</v>
+        <v>38.39850496690529</v>
       </c>
       <c r="E9">
-        <v>3.472</v>
+        <v>3.968</v>
       </c>
       <c r="F9">
-        <v>3.472</v>
+        <v>3.968</v>
       </c>
       <c r="G9">
         <v>12.4</v>
@@ -2025,28 +2025,28 @@
         <v>6.62</v>
       </c>
       <c r="M9">
-        <v>0.1746416</v>
+        <v>0.1995904</v>
       </c>
       <c r="N9">
-        <v>6.4453584</v>
+        <v>6.4204096</v>
       </c>
       <c r="O9">
-        <v>1.740246768</v>
+        <v>1.733510592</v>
       </c>
       <c r="P9">
-        <v>4.705111631999999</v>
+        <v>4.686899008</v>
       </c>
       <c r="Q9">
-        <v>5.875111631999999</v>
+        <v>5.856899008</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1255310502148411</v>
+        <v>0.1261758861649152</v>
       </c>
       <c r="T9">
-        <v>0.9551574368383298</v>
+        <v>0.9628824053618147</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.90620333299741</v>
+        <v>33.16792791637273</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.119019335271722</v>
+        <v>0.1187244638436419</v>
       </c>
       <c r="C10">
-        <v>46.83050496690529</v>
+        <v>46.48977003707449</v>
       </c>
       <c r="D10">
-        <v>38.39850496690529</v>
+        <v>38.55377003707449</v>
       </c>
       <c r="E10">
-        <v>3.968</v>
+        <v>4.464</v>
       </c>
       <c r="F10">
-        <v>3.968</v>
+        <v>4.464</v>
       </c>
       <c r="G10">
         <v>12.4</v>
@@ -2107,28 +2107,28 @@
         <v>6.62</v>
       </c>
       <c r="M10">
-        <v>0.1995904</v>
+        <v>0.2245392</v>
       </c>
       <c r="N10">
-        <v>6.4204096</v>
+        <v>6.3954608</v>
       </c>
       <c r="O10">
-        <v>1.733510592</v>
+        <v>1.726774416</v>
       </c>
       <c r="P10">
-        <v>4.686899008</v>
+        <v>4.668686384</v>
       </c>
       <c r="Q10">
-        <v>5.856899008</v>
+        <v>5.838686384</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1261758861649152</v>
+        <v>0.1268348943336724</v>
       </c>
       <c r="T10">
-        <v>0.9628824053618147</v>
+        <v>0.9707771534132884</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.16792791637273</v>
+        <v>29.48260259233132</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1187244638436419</v>
+        <v>0.1184295924155617</v>
       </c>
       <c r="C11">
-        <v>46.48977003707449</v>
+        <v>46.15029583944526</v>
       </c>
       <c r="D11">
-        <v>38.55377003707449</v>
+        <v>38.71029583944526</v>
       </c>
       <c r="E11">
-        <v>4.464</v>
+        <v>4.96</v>
       </c>
       <c r="F11">
-        <v>4.464</v>
+        <v>4.96</v>
       </c>
       <c r="G11">
         <v>12.4</v>
@@ -2189,28 +2189,28 @@
         <v>6.62</v>
       </c>
       <c r="M11">
-        <v>0.2245392</v>
+        <v>0.249488</v>
       </c>
       <c r="N11">
-        <v>6.3954608</v>
+        <v>6.370512</v>
       </c>
       <c r="O11">
-        <v>1.726774416</v>
+        <v>1.72003824</v>
       </c>
       <c r="P11">
-        <v>4.668686384</v>
+        <v>4.65047376</v>
       </c>
       <c r="Q11">
-        <v>5.838686384</v>
+        <v>5.82047376</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1268348943336724</v>
+        <v>0.1275085471284018</v>
       </c>
       <c r="T11">
-        <v>0.9707771534132884</v>
+        <v>0.9788473403103504</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.48260259233132</v>
+        <v>26.53434233309818</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1184295924155617</v>
+        <v>0.1181347209874815</v>
       </c>
       <c r="C12">
-        <v>46.15029583944526</v>
+        <v>45.8120977920865</v>
       </c>
       <c r="D12">
-        <v>38.71029583944526</v>
+        <v>38.86809779208651</v>
       </c>
       <c r="E12">
-        <v>4.960000000000001</v>
+        <v>5.456</v>
       </c>
       <c r="F12">
-        <v>4.960000000000001</v>
+        <v>5.456</v>
       </c>
       <c r="G12">
         <v>12.4</v>
@@ -2271,28 +2271,28 @@
         <v>6.62</v>
       </c>
       <c r="M12">
-        <v>0.249488</v>
+        <v>0.2744368</v>
       </c>
       <c r="N12">
-        <v>6.370512</v>
+        <v>6.3455632</v>
       </c>
       <c r="O12">
-        <v>1.72003824</v>
+        <v>1.713302064</v>
       </c>
       <c r="P12">
-        <v>4.65047376</v>
+        <v>4.632261136</v>
       </c>
       <c r="Q12">
-        <v>5.82047376</v>
+        <v>5.802261136</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1275085471284018</v>
+        <v>0.1281973381881814</v>
       </c>
       <c r="T12">
-        <v>0.9788473403103504</v>
+        <v>0.987098879721953</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.53434233309818</v>
+        <v>24.12212939372563</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1181347209874815</v>
+        <v>0.1178398495594013</v>
       </c>
       <c r="C13">
-        <v>45.8120977920865</v>
+        <v>45.47519156550231</v>
       </c>
       <c r="D13">
-        <v>38.86809779208651</v>
+        <v>39.02719156550231</v>
       </c>
       <c r="E13">
-        <v>5.456</v>
+        <v>5.952</v>
       </c>
       <c r="F13">
-        <v>5.456</v>
+        <v>5.952</v>
       </c>
       <c r="G13">
         <v>12.4</v>
@@ -2353,28 +2353,28 @@
         <v>6.62</v>
       </c>
       <c r="M13">
-        <v>0.2744368</v>
+        <v>0.2993856</v>
       </c>
       <c r="N13">
-        <v>6.3455632</v>
+        <v>6.3206144</v>
       </c>
       <c r="O13">
-        <v>1.713302064</v>
+        <v>1.706565888</v>
       </c>
       <c r="P13">
-        <v>4.632261136</v>
+        <v>4.614048512</v>
       </c>
       <c r="Q13">
-        <v>5.802261136</v>
+        <v>5.784048512</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1281973381881814</v>
+        <v>0.1289017835902287</v>
       </c>
       <c r="T13">
-        <v>0.987098879721953</v>
+        <v>0.995537954120183</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.12212939372563</v>
+        <v>22.11195194424849</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1178398495594013</v>
+        <v>0.1175449781313211</v>
       </c>
       <c r="C14">
-        <v>45.47519156550231</v>
+        <v>45.13959308781952</v>
       </c>
       <c r="D14">
-        <v>39.02719156550231</v>
+        <v>39.18759308781952</v>
       </c>
       <c r="E14">
-        <v>5.952</v>
+        <v>6.448</v>
       </c>
       <c r="F14">
-        <v>5.952</v>
+        <v>6.448</v>
       </c>
       <c r="G14">
         <v>12.4</v>
@@ -2435,28 +2435,28 @@
         <v>6.62</v>
       </c>
       <c r="M14">
-        <v>0.2993856</v>
+        <v>0.3243344</v>
       </c>
       <c r="N14">
-        <v>6.3206144</v>
+        <v>6.2956656</v>
       </c>
       <c r="O14">
-        <v>1.706565888</v>
+        <v>1.699829712</v>
       </c>
       <c r="P14">
-        <v>4.614048512</v>
+        <v>4.595835888</v>
       </c>
       <c r="Q14">
-        <v>5.784048512</v>
+        <v>5.765835888</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1289017835902287</v>
+        <v>0.1296224231394495</v>
       </c>
       <c r="T14">
-        <v>0.995537954120183</v>
+        <v>1.004171030228717</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.11195194424849</v>
+        <v>20.41103256392168</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1175449781313211</v>
+        <v>0.1172501067032409</v>
       </c>
       <c r="C15">
-        <v>45.13959308781952</v>
+        <v>44.80531855010362</v>
       </c>
       <c r="D15">
-        <v>39.18759308781952</v>
+        <v>39.34931855010363</v>
       </c>
       <c r="E15">
-        <v>6.448</v>
+        <v>6.944000000000001</v>
       </c>
       <c r="F15">
-        <v>6.448</v>
+        <v>6.944000000000001</v>
       </c>
       <c r="G15">
         <v>12.4</v>
@@ -2517,28 +2517,28 @@
         <v>6.62</v>
       </c>
       <c r="M15">
-        <v>0.3243344</v>
+        <v>0.3492832</v>
       </c>
       <c r="N15">
-        <v>6.2956656</v>
+        <v>6.2707168</v>
       </c>
       <c r="O15">
-        <v>1.699829712</v>
+        <v>1.693093536</v>
       </c>
       <c r="P15">
-        <v>4.595835888</v>
+        <v>4.577623264</v>
       </c>
       <c r="Q15">
-        <v>5.765835888</v>
+        <v>5.747623264</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1296224231394495</v>
+        <v>0.1303598217479546</v>
       </c>
       <c r="T15">
-        <v>1.004171030228717</v>
+        <v>1.013004875549077</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.41103256392168</v>
+        <v>18.9531016664987</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1172501067032409</v>
+        <v>0.1169552352751607</v>
       </c>
       <c r="C16">
-        <v>44.80531855010362</v>
+        <v>44.47238441180701</v>
       </c>
       <c r="D16">
-        <v>39.34931855010363</v>
+        <v>39.51238441180701</v>
       </c>
       <c r="E16">
-        <v>6.944000000000001</v>
+        <v>7.440000000000001</v>
       </c>
       <c r="F16">
-        <v>6.944000000000001</v>
+        <v>7.440000000000001</v>
       </c>
       <c r="G16">
         <v>12.4</v>
@@ -2599,28 +2599,28 @@
         <v>6.62</v>
       </c>
       <c r="M16">
-        <v>0.3492832</v>
+        <v>0.3742320000000001</v>
       </c>
       <c r="N16">
-        <v>6.2707168</v>
+        <v>6.245768</v>
       </c>
       <c r="O16">
-        <v>1.693093536</v>
+        <v>1.68635736</v>
       </c>
       <c r="P16">
-        <v>4.577623264</v>
+        <v>4.559410639999999</v>
       </c>
       <c r="Q16">
-        <v>5.747623264</v>
+        <v>5.729410639999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1303598217479546</v>
+        <v>0.1311145709119538</v>
       </c>
       <c r="T16">
-        <v>1.013004875549077</v>
+        <v>1.022046576053447</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.9531016664987</v>
+        <v>17.68956155539879</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1169552352751607</v>
+        <v>0.1166603638470806</v>
       </c>
       <c r="C17">
-        <v>44.47238441180701</v>
+        <v>44.14080740635309</v>
       </c>
       <c r="D17">
-        <v>39.51238441180701</v>
+        <v>39.67680740635309</v>
       </c>
       <c r="E17">
-        <v>7.44</v>
+        <v>7.936000000000001</v>
       </c>
       <c r="F17">
-        <v>7.44</v>
+        <v>7.936000000000001</v>
       </c>
       <c r="G17">
         <v>12.4</v>
@@ -2681,28 +2681,28 @@
         <v>6.62</v>
       </c>
       <c r="M17">
-        <v>0.374232</v>
+        <v>0.3991808</v>
       </c>
       <c r="N17">
-        <v>6.245768</v>
+        <v>6.2208192</v>
       </c>
       <c r="O17">
-        <v>1.68635736</v>
+        <v>1.679621184</v>
       </c>
       <c r="P17">
-        <v>4.559410639999999</v>
+        <v>4.541198016</v>
       </c>
       <c r="Q17">
-        <v>5.729410639999999</v>
+        <v>5.711198016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1311145709119538</v>
+        <v>0.1318872902941436</v>
       </c>
       <c r="T17">
-        <v>1.022046576053447</v>
+        <v>1.031303555141253</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.68956155539879</v>
+        <v>16.58396395818637</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1166603638470806</v>
+        <v>0.1163654924190004</v>
       </c>
       <c r="C18">
-        <v>44.14080740635309</v>
+        <v>43.81060454686058</v>
       </c>
       <c r="D18">
-        <v>39.67680740635309</v>
+        <v>39.84260454686058</v>
       </c>
       <c r="E18">
-        <v>7.936000000000001</v>
+        <v>8.432</v>
       </c>
       <c r="F18">
-        <v>7.936000000000001</v>
+        <v>8.432</v>
       </c>
       <c r="G18">
         <v>12.4</v>
@@ -2763,28 +2763,28 @@
         <v>6.62</v>
       </c>
       <c r="M18">
-        <v>0.3991808</v>
+        <v>0.4241296</v>
       </c>
       <c r="N18">
-        <v>6.2208192</v>
+        <v>6.1958704</v>
       </c>
       <c r="O18">
-        <v>1.679621184</v>
+        <v>1.672885008</v>
       </c>
       <c r="P18">
-        <v>4.541198016</v>
+        <v>4.522985392000001</v>
       </c>
       <c r="Q18">
-        <v>5.711198016</v>
+        <v>5.692985392000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1318872902941436</v>
+        <v>0.1326786294204824</v>
       </c>
       <c r="T18">
-        <v>1.031303555141253</v>
+        <v>1.040783593966115</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.58396395818637</v>
+        <v>15.60843666652834</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1163654924190004</v>
+        <v>0.1160706209909202</v>
       </c>
       <c r="C19">
-        <v>43.81060454686058</v>
+        <v>43.48179313201177</v>
       </c>
       <c r="D19">
-        <v>39.84260454686058</v>
+        <v>40.00979313201177</v>
       </c>
       <c r="E19">
-        <v>8.432</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="F19">
-        <v>8.432</v>
+        <v>8.928000000000001</v>
       </c>
       <c r="G19">
         <v>12.4</v>
@@ -2845,28 +2845,28 @@
         <v>6.62</v>
       </c>
       <c r="M19">
-        <v>0.4241296</v>
+        <v>0.4490784</v>
       </c>
       <c r="N19">
-        <v>6.1958704</v>
+        <v>6.1709216</v>
       </c>
       <c r="O19">
-        <v>1.672885008</v>
+        <v>1.666148832</v>
       </c>
       <c r="P19">
-        <v>4.522985392000001</v>
+        <v>4.504772768</v>
       </c>
       <c r="Q19">
-        <v>5.692985392000001</v>
+        <v>5.674772768</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1326786294204824</v>
+        <v>0.1334892695011222</v>
       </c>
       <c r="T19">
-        <v>1.040783593966115</v>
+        <v>1.05049485325012</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.60843666652834</v>
+        <v>14.74130129616566</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1160706209909202</v>
+        <v>0.11577574956284</v>
       </c>
       <c r="C20">
-        <v>43.48179313201176</v>
+        <v>43.1543907520692</v>
       </c>
       <c r="D20">
-        <v>40.00979313201176</v>
+        <v>40.17839075206921</v>
       </c>
       <c r="E20">
-        <v>8.927999999999999</v>
+        <v>9.424000000000001</v>
       </c>
       <c r="F20">
-        <v>8.927999999999999</v>
+        <v>9.424000000000001</v>
       </c>
       <c r="G20">
         <v>12.4</v>
@@ -2927,28 +2927,28 @@
         <v>6.62</v>
       </c>
       <c r="M20">
-        <v>0.4490783999999999</v>
+        <v>0.4740272</v>
       </c>
       <c r="N20">
-        <v>6.1709216</v>
+        <v>6.1459728</v>
       </c>
       <c r="O20">
-        <v>1.666148832</v>
+        <v>1.659412656</v>
       </c>
       <c r="P20">
-        <v>4.504772768</v>
+        <v>4.486560144</v>
       </c>
       <c r="Q20">
-        <v>5.674772768</v>
+        <v>5.656560144</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1334892695011222</v>
+        <v>0.1343199253862223</v>
       </c>
       <c r="T20">
-        <v>1.05049485325012</v>
+        <v>1.060445896713977</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.74130129616566</v>
+        <v>13.96544333320957</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.11577574956284</v>
+        <v>0.1154808781347599</v>
       </c>
       <c r="C21">
-        <v>43.1543907520692</v>
+        <v>42.82841529504515</v>
       </c>
       <c r="D21">
-        <v>40.17839075206921</v>
+        <v>40.34841529504515</v>
       </c>
       <c r="E21">
-        <v>9.424000000000001</v>
+        <v>9.920000000000002</v>
       </c>
       <c r="F21">
-        <v>9.424000000000001</v>
+        <v>9.920000000000002</v>
       </c>
       <c r="G21">
         <v>12.4</v>
@@ -3009,28 +3009,28 @@
         <v>6.62</v>
       </c>
       <c r="M21">
-        <v>0.4740272</v>
+        <v>0.4989760000000001</v>
       </c>
       <c r="N21">
-        <v>6.1459728</v>
+        <v>6.121024</v>
       </c>
       <c r="O21">
-        <v>1.659412656</v>
+        <v>1.65267648</v>
       </c>
       <c r="P21">
-        <v>4.486560144</v>
+        <v>4.46834752</v>
       </c>
       <c r="Q21">
-        <v>5.656560144</v>
+        <v>5.63834752</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1343199253862223</v>
+        <v>0.1351713476684498</v>
       </c>
       <c r="T21">
-        <v>1.060445896713977</v>
+        <v>1.07064571626443</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.96544333320957</v>
+        <v>13.26717116654909</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1154808781347599</v>
+        <v>0.1154159567066797</v>
       </c>
       <c r="C22">
-        <v>42.82841529504515</v>
+        <v>42.3700428285252</v>
       </c>
       <c r="D22">
-        <v>40.34841529504515</v>
+        <v>40.38604282852521</v>
       </c>
       <c r="E22">
-        <v>9.920000000000002</v>
+        <v>10.416</v>
       </c>
       <c r="F22">
-        <v>9.920000000000002</v>
+        <v>10.416</v>
       </c>
       <c r="G22">
         <v>12.4</v>
@@ -3091,45 +3091,45 @@
         <v>6.62</v>
       </c>
       <c r="M22">
-        <v>0.4989760000000001</v>
+        <v>0.5395488000000001</v>
       </c>
       <c r="N22">
-        <v>6.121024</v>
+        <v>6.0804512</v>
       </c>
       <c r="O22">
-        <v>1.65267648</v>
+        <v>1.641721824</v>
       </c>
       <c r="P22">
-        <v>4.46834752</v>
+        <v>4.438729376</v>
       </c>
       <c r="Q22">
-        <v>5.63834752</v>
+        <v>5.608729375999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1351713476684498</v>
+        <v>0.1360443249451641</v>
       </c>
       <c r="T22">
-        <v>1.07064571626443</v>
+        <v>1.081103759094642</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.27</v>
       </c>
       <c r="W22">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.26717116654909</v>
+        <v>12.26951111743738</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1154159567066797</v>
+        <v>0.1151320352785995</v>
       </c>
       <c r="C23">
-        <v>42.3700428285252</v>
+        <v>42.03942760207622</v>
       </c>
       <c r="D23">
-        <v>40.38604282852521</v>
+        <v>40.55142760207622</v>
       </c>
       <c r="E23">
-        <v>10.416</v>
+        <v>10.912</v>
       </c>
       <c r="F23">
-        <v>10.416</v>
+        <v>10.912</v>
       </c>
       <c r="G23">
         <v>12.4</v>
@@ -3173,28 +3173,28 @@
         <v>6.62</v>
       </c>
       <c r="M23">
-        <v>0.5395488000000001</v>
+        <v>0.5652416</v>
       </c>
       <c r="N23">
-        <v>6.0804512</v>
+        <v>6.0547584</v>
       </c>
       <c r="O23">
-        <v>1.641721824</v>
+        <v>1.634784768</v>
       </c>
       <c r="P23">
-        <v>4.438729376</v>
+        <v>4.419973632</v>
       </c>
       <c r="Q23">
-        <v>5.608729375999999</v>
+        <v>5.589973632</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1360443249451641</v>
+        <v>0.1369396862546147</v>
       </c>
       <c r="T23">
-        <v>1.081103759094642</v>
+        <v>1.091829956869218</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.26951111743738</v>
+        <v>11.71180606664478</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1151320352785995</v>
+        <v>0.1148481138505193</v>
       </c>
       <c r="C24">
-        <v>42.03942760207622</v>
+        <v>41.71017247885006</v>
       </c>
       <c r="D24">
-        <v>40.55142760207622</v>
+        <v>40.71817247885006</v>
       </c>
       <c r="E24">
-        <v>10.912</v>
+        <v>11.408</v>
       </c>
       <c r="F24">
-        <v>10.912</v>
+        <v>11.408</v>
       </c>
       <c r="G24">
         <v>12.4</v>
@@ -3255,28 +3255,28 @@
         <v>6.62</v>
       </c>
       <c r="M24">
-        <v>0.5652416</v>
+        <v>0.5909344000000001</v>
       </c>
       <c r="N24">
-        <v>6.0547584</v>
+        <v>6.0290656</v>
       </c>
       <c r="O24">
-        <v>1.634784768</v>
+        <v>1.627847712</v>
       </c>
       <c r="P24">
-        <v>4.419973632</v>
+        <v>4.401217888</v>
       </c>
       <c r="Q24">
-        <v>5.589973632</v>
+        <v>5.571217888</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1369396862546147</v>
+        <v>0.1378583037019731</v>
       </c>
       <c r="T24">
-        <v>1.091829956869218</v>
+        <v>1.102834757183393</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.71180606664478</v>
+        <v>11.20259710722544</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1148481138505193</v>
+        <v>0.1145641924224391</v>
       </c>
       <c r="C25">
-        <v>41.71017247885006</v>
+        <v>41.38229430609394</v>
       </c>
       <c r="D25">
-        <v>40.71817247885006</v>
+        <v>40.88629430609394</v>
       </c>
       <c r="E25">
-        <v>11.408</v>
+        <v>11.904</v>
       </c>
       <c r="F25">
-        <v>11.408</v>
+        <v>11.904</v>
       </c>
       <c r="G25">
         <v>12.4</v>
@@ -3337,28 +3337,28 @@
         <v>6.62</v>
       </c>
       <c r="M25">
-        <v>0.5909344000000001</v>
+        <v>0.6166272</v>
       </c>
       <c r="N25">
-        <v>6.0290656</v>
+        <v>6.0033728</v>
       </c>
       <c r="O25">
-        <v>1.627847712</v>
+        <v>1.620910656</v>
       </c>
       <c r="P25">
-        <v>4.401217888</v>
+        <v>4.382462144</v>
       </c>
       <c r="Q25">
-        <v>5.571217888</v>
+        <v>5.552462144</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1378583037019731</v>
+        <v>0.1388010952926831</v>
       </c>
       <c r="T25">
-        <v>1.102834757183393</v>
+        <v>1.114129157505836</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.20259710722544</v>
+        <v>10.73582222775771</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1145641924224391</v>
+        <v>0.1142802709943589</v>
       </c>
       <c r="C26">
-        <v>41.38229430609394</v>
+        <v>41.05581021045199</v>
       </c>
       <c r="D26">
-        <v>40.88629430609394</v>
+        <v>41.05581021045199</v>
       </c>
       <c r="E26">
-        <v>11.904</v>
+        <v>12.4</v>
       </c>
       <c r="F26">
-        <v>11.904</v>
+        <v>12.4</v>
       </c>
       <c r="G26">
         <v>12.4</v>
@@ -3419,28 +3419,28 @@
         <v>6.62</v>
       </c>
       <c r="M26">
-        <v>0.6166271999999999</v>
+        <v>0.64232</v>
       </c>
       <c r="N26">
-        <v>6.0033728</v>
+        <v>5.97768</v>
       </c>
       <c r="O26">
-        <v>1.620910656</v>
+        <v>1.6139736</v>
       </c>
       <c r="P26">
-        <v>4.382462144</v>
+        <v>4.3637064</v>
       </c>
       <c r="Q26">
-        <v>5.552462144</v>
+        <v>5.5337064</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1388010952926831</v>
+        <v>0.1397690279924786</v>
       </c>
       <c r="T26">
-        <v>1.114129157505836</v>
+        <v>1.125724741836878</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.73582222775771</v>
+        <v>10.3063893386474</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1142802709943589</v>
+        <v>0.1139963495662788</v>
       </c>
       <c r="C27">
-        <v>41.05581021045199</v>
+        <v>40.73073760378134</v>
       </c>
       <c r="D27">
-        <v>41.05581021045199</v>
+        <v>41.22673760378134</v>
       </c>
       <c r="E27">
-        <v>12.4</v>
+        <v>12.896</v>
       </c>
       <c r="F27">
-        <v>12.4</v>
+        <v>12.896</v>
       </c>
       <c r="G27">
         <v>12.4</v>
@@ -3501,28 +3501,28 @@
         <v>6.62</v>
       </c>
       <c r="M27">
-        <v>0.64232</v>
+        <v>0.6680128000000001</v>
       </c>
       <c r="N27">
-        <v>5.97768</v>
+        <v>5.9519872</v>
       </c>
       <c r="O27">
-        <v>1.6139736</v>
+        <v>1.607036544</v>
       </c>
       <c r="P27">
-        <v>4.3637064</v>
+        <v>4.344950656</v>
       </c>
       <c r="Q27">
-        <v>5.5337064</v>
+        <v>5.514950656</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1397690279924786</v>
+        <v>0.1407631210355118</v>
       </c>
       <c r="T27">
-        <v>1.125724741836878</v>
+        <v>1.137633720339029</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.3063893386474</v>
+        <v>9.909989748699424</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1139963495662788</v>
+        <v>0.1140474981381986</v>
       </c>
       <c r="C28">
-        <v>40.73073760378134</v>
+        <v>40.20383993264508</v>
       </c>
       <c r="D28">
-        <v>41.22673760378134</v>
+        <v>41.19583993264509</v>
       </c>
       <c r="E28">
-        <v>12.896</v>
+        <v>13.392</v>
       </c>
       <c r="F28">
-        <v>12.896</v>
+        <v>13.392</v>
       </c>
       <c r="G28">
         <v>12.4</v>
@@ -3583,45 +3583,45 @@
         <v>6.62</v>
       </c>
       <c r="M28">
-        <v>0.6680128000000001</v>
+        <v>0.716472</v>
       </c>
       <c r="N28">
-        <v>5.9519872</v>
+        <v>5.903528</v>
       </c>
       <c r="O28">
-        <v>1.607036544</v>
+        <v>1.59395256</v>
       </c>
       <c r="P28">
-        <v>4.344950656</v>
+        <v>4.30957544</v>
       </c>
       <c r="Q28">
-        <v>5.514950656</v>
+        <v>5.47957544</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1407631210355118</v>
+        <v>0.1417844495043816</v>
       </c>
       <c r="T28">
-        <v>1.137633720339029</v>
+        <v>1.1498689722248</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.27</v>
       </c>
       <c r="W28">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.909989748699424</v>
+        <v>9.239719067877042</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1140474981381986</v>
+        <v>0.1137759867101184</v>
       </c>
       <c r="C29">
-        <v>40.20383993264508</v>
+        <v>39.8723854121947</v>
       </c>
       <c r="D29">
-        <v>41.19583993264509</v>
+        <v>41.3603854121947</v>
       </c>
       <c r="E29">
-        <v>13.392</v>
+        <v>13.888</v>
       </c>
       <c r="F29">
-        <v>13.392</v>
+        <v>13.888</v>
       </c>
       <c r="G29">
         <v>12.4</v>
@@ -3665,28 +3665,28 @@
         <v>6.62</v>
       </c>
       <c r="M29">
-        <v>0.716472</v>
+        <v>0.7430080000000001</v>
       </c>
       <c r="N29">
-        <v>5.903528</v>
+        <v>5.876992</v>
       </c>
       <c r="O29">
-        <v>1.59395256</v>
+        <v>1.58678784</v>
       </c>
       <c r="P29">
-        <v>4.30957544</v>
+        <v>4.29020416</v>
       </c>
       <c r="Q29">
-        <v>5.47957544</v>
+        <v>5.46020416</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1417844495043816</v>
+        <v>0.1428341482084978</v>
       </c>
       <c r="T29">
-        <v>1.1498689722248</v>
+        <v>1.16244409221851</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.239719067877042</v>
+        <v>8.909729101167146</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1137759867101184</v>
+        <v>0.1135044752820382</v>
       </c>
       <c r="C30">
-        <v>39.8723854121947</v>
+        <v>39.54225062660529</v>
       </c>
       <c r="D30">
-        <v>41.3603854121947</v>
+        <v>41.52625062660529</v>
       </c>
       <c r="E30">
-        <v>13.888</v>
+        <v>14.384</v>
       </c>
       <c r="F30">
-        <v>13.888</v>
+        <v>14.384</v>
       </c>
       <c r="G30">
         <v>12.4</v>
@@ -3747,28 +3747,28 @@
         <v>6.62</v>
       </c>
       <c r="M30">
-        <v>0.7430080000000001</v>
+        <v>0.7695440000000001</v>
       </c>
       <c r="N30">
-        <v>5.876992</v>
+        <v>5.850456</v>
       </c>
       <c r="O30">
-        <v>1.58678784</v>
+        <v>1.57962312</v>
       </c>
       <c r="P30">
-        <v>4.29020416</v>
+        <v>4.27083288</v>
       </c>
       <c r="Q30">
-        <v>5.46020416</v>
+        <v>5.44083288</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1428341482084978</v>
+        <v>0.1439134158901947</v>
       </c>
       <c r="T30">
-        <v>1.16244409221851</v>
+        <v>1.175373440944436</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.909729101167146</v>
+        <v>8.602497063195866</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1135044752820382</v>
+        <v>0.113232963853958</v>
       </c>
       <c r="C31">
-        <v>39.54225062660529</v>
+        <v>39.21345151717956</v>
       </c>
       <c r="D31">
-        <v>41.52625062660529</v>
+        <v>41.69345151717957</v>
       </c>
       <c r="E31">
-        <v>14.384</v>
+        <v>14.88</v>
       </c>
       <c r="F31">
-        <v>14.384</v>
+        <v>14.88</v>
       </c>
       <c r="G31">
         <v>12.4</v>
@@ -3829,28 +3829,28 @@
         <v>6.62</v>
       </c>
       <c r="M31">
-        <v>0.7695439999999999</v>
+        <v>0.7960799999999999</v>
       </c>
       <c r="N31">
-        <v>5.850456</v>
+        <v>5.82392</v>
       </c>
       <c r="O31">
-        <v>1.57962312</v>
+        <v>1.5724584</v>
       </c>
       <c r="P31">
-        <v>4.27083288</v>
+        <v>4.2514616</v>
       </c>
       <c r="Q31">
-        <v>5.44083288</v>
+        <v>5.4214616</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1439134158901947</v>
+        <v>0.1450235197913686</v>
       </c>
       <c r="T31">
-        <v>1.175373440944436</v>
+        <v>1.188672199633961</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.602497063195868</v>
+        <v>8.315747161089339</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.113232963853958</v>
+        <v>0.1129614524258779</v>
       </c>
       <c r="C32">
-        <v>39.21345151717956</v>
+        <v>38.88600428300183</v>
       </c>
       <c r="D32">
-        <v>41.69345151717957</v>
+        <v>41.86200428300183</v>
       </c>
       <c r="E32">
-        <v>14.88</v>
+        <v>15.376</v>
       </c>
       <c r="F32">
-        <v>14.88</v>
+        <v>15.376</v>
       </c>
       <c r="G32">
         <v>12.4</v>
@@ -3911,28 +3911,28 @@
         <v>6.62</v>
       </c>
       <c r="M32">
-        <v>0.7960799999999999</v>
+        <v>0.8226159999999999</v>
       </c>
       <c r="N32">
-        <v>5.82392</v>
+        <v>5.797384</v>
       </c>
       <c r="O32">
-        <v>1.5724584</v>
+        <v>1.56529368</v>
       </c>
       <c r="P32">
-        <v>4.2514616</v>
+        <v>4.23209032</v>
       </c>
       <c r="Q32">
-        <v>5.4214616</v>
+        <v>5.40209032</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1450235197913686</v>
+        <v>0.1461658006172143</v>
       </c>
       <c r="T32">
-        <v>1.188672199633961</v>
+        <v>1.202356429589849</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.315747161089339</v>
+        <v>8.047497252667103</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1129614524258779</v>
+        <v>0.1126899409977977</v>
       </c>
       <c r="C33">
-        <v>38.88600428300183</v>
+        <v>38.55992538616965</v>
       </c>
       <c r="D33">
-        <v>41.86200428300183</v>
+        <v>42.03192538616965</v>
       </c>
       <c r="E33">
-        <v>15.376</v>
+        <v>15.872</v>
       </c>
       <c r="F33">
-        <v>15.376</v>
+        <v>15.872</v>
       </c>
       <c r="G33">
         <v>12.4</v>
@@ -3993,28 +3993,28 @@
         <v>6.62</v>
       </c>
       <c r="M33">
-        <v>0.8226159999999999</v>
+        <v>0.849152</v>
       </c>
       <c r="N33">
-        <v>5.797384</v>
+        <v>5.770848</v>
       </c>
       <c r="O33">
-        <v>1.56529368</v>
+        <v>1.55812896</v>
       </c>
       <c r="P33">
-        <v>4.23209032</v>
+        <v>4.21271904</v>
       </c>
       <c r="Q33">
-        <v>5.40209032</v>
+        <v>5.38271904</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1461658006172143</v>
+        <v>0.1473416779379378</v>
       </c>
       <c r="T33">
-        <v>1.202356429589849</v>
+        <v>1.21644313689738</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.047497252667103</v>
+        <v>7.796012963521254</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1126899409977977</v>
+        <v>0.1126111495697175</v>
       </c>
       <c r="C34">
-        <v>38.55992538616965</v>
+        <v>38.11349428967549</v>
       </c>
       <c r="D34">
-        <v>42.03192538616965</v>
+        <v>42.0814942896755</v>
       </c>
       <c r="E34">
-        <v>15.872</v>
+        <v>16.368</v>
       </c>
       <c r="F34">
-        <v>15.872</v>
+        <v>16.368</v>
       </c>
       <c r="G34">
         <v>12.4</v>
@@ -4075,45 +4075,45 @@
         <v>6.62</v>
       </c>
       <c r="M34">
-        <v>0.849152</v>
+        <v>0.8887824000000001</v>
       </c>
       <c r="N34">
-        <v>5.770848</v>
+        <v>5.7312176</v>
       </c>
       <c r="O34">
-        <v>1.55812896</v>
+        <v>1.547428752</v>
       </c>
       <c r="P34">
-        <v>4.21271904</v>
+        <v>4.183788848</v>
       </c>
       <c r="Q34">
-        <v>5.38271904</v>
+        <v>5.353788848</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1473416779379378</v>
+        <v>0.1485526560742052</v>
       </c>
       <c r="T34">
-        <v>1.21644313689738</v>
+        <v>1.230950342930509</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.27</v>
       </c>
       <c r="W34">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.796012963521254</v>
+        <v>7.448392317399624</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1126111495697175</v>
+        <v>0.1123454781416373</v>
       </c>
       <c r="C35">
-        <v>38.11349428967549</v>
+        <v>37.78549745076018</v>
       </c>
       <c r="D35">
-        <v>42.0814942896755</v>
+        <v>42.24949745076017</v>
       </c>
       <c r="E35">
-        <v>16.368</v>
+        <v>16.864</v>
       </c>
       <c r="F35">
-        <v>16.368</v>
+        <v>16.864</v>
       </c>
       <c r="G35">
         <v>12.4</v>
@@ -4157,28 +4157,28 @@
         <v>6.62</v>
       </c>
       <c r="M35">
-        <v>0.8887824000000001</v>
+        <v>0.9157152000000001</v>
       </c>
       <c r="N35">
-        <v>5.7312176</v>
+        <v>5.7042848</v>
       </c>
       <c r="O35">
-        <v>1.547428752</v>
+        <v>1.540156896</v>
       </c>
       <c r="P35">
-        <v>4.183788848</v>
+        <v>4.164127904</v>
       </c>
       <c r="Q35">
-        <v>5.353788848</v>
+        <v>5.334127904</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1485526560742052</v>
+        <v>0.1498003305176323</v>
       </c>
       <c r="T35">
-        <v>1.230950342930509</v>
+        <v>1.245897161267673</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.448392317399624</v>
+        <v>7.229321955123164</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1123454781416373</v>
+        <v>0.1120798067135571</v>
       </c>
       <c r="C36">
-        <v>37.78549745076018</v>
+        <v>37.45884743652465</v>
       </c>
       <c r="D36">
-        <v>42.24949745076017</v>
+        <v>42.41884743652465</v>
       </c>
       <c r="E36">
-        <v>16.864</v>
+        <v>17.36</v>
       </c>
       <c r="F36">
-        <v>16.864</v>
+        <v>17.36</v>
       </c>
       <c r="G36">
         <v>12.4</v>
@@ -4239,28 +4239,28 @@
         <v>6.62</v>
       </c>
       <c r="M36">
-        <v>0.9157152000000001</v>
+        <v>0.9426480000000002</v>
       </c>
       <c r="N36">
-        <v>5.7042848</v>
+        <v>5.677352</v>
       </c>
       <c r="O36">
-        <v>1.540156896</v>
+        <v>1.53288504</v>
       </c>
       <c r="P36">
-        <v>4.164127904</v>
+        <v>4.14446696</v>
       </c>
       <c r="Q36">
-        <v>5.334127904</v>
+        <v>5.31446696</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1498003305176323</v>
+        <v>0.1510863949439341</v>
       </c>
       <c r="T36">
-        <v>1.245897161267673</v>
+        <v>1.261303881707518</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.229321955123164</v>
+        <v>7.022769899262502</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1120798067135571</v>
+        <v>0.1118141352854769</v>
       </c>
       <c r="C37">
-        <v>37.45884743652465</v>
+        <v>37.13356050770619</v>
       </c>
       <c r="D37">
-        <v>42.41884743652465</v>
+        <v>42.58956050770619</v>
       </c>
       <c r="E37">
-        <v>17.36</v>
+        <v>17.856</v>
       </c>
       <c r="F37">
-        <v>17.36</v>
+        <v>17.856</v>
       </c>
       <c r="G37">
         <v>12.4</v>
@@ -4321,28 +4321,28 @@
         <v>6.62</v>
       </c>
       <c r="M37">
-        <v>0.9426480000000002</v>
+        <v>0.9695808000000001</v>
       </c>
       <c r="N37">
-        <v>5.677352</v>
+        <v>5.6504192</v>
       </c>
       <c r="O37">
-        <v>1.53288504</v>
+        <v>1.525613184</v>
       </c>
       <c r="P37">
-        <v>4.14446696</v>
+        <v>4.124806016</v>
       </c>
       <c r="Q37">
-        <v>5.31446696</v>
+        <v>5.294806016</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1510863949439341</v>
+        <v>0.1524126488835577</v>
       </c>
       <c r="T37">
-        <v>1.261303881707518</v>
+        <v>1.277192062161109</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.022769899262502</v>
+        <v>6.827692957616321</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.111814135285477</v>
+        <v>0.1115484638573968</v>
       </c>
       <c r="C38">
-        <v>37.13356050770618</v>
+        <v>36.80965318786265</v>
       </c>
       <c r="D38">
-        <v>42.58956050770617</v>
+        <v>42.76165318786265</v>
       </c>
       <c r="E38">
-        <v>17.856</v>
+        <v>18.352</v>
       </c>
       <c r="F38">
-        <v>17.856</v>
+        <v>18.352</v>
       </c>
       <c r="G38">
         <v>12.4</v>
@@ -4403,28 +4403,28 @@
         <v>6.62</v>
       </c>
       <c r="M38">
-        <v>0.9695807999999999</v>
+        <v>0.9965136</v>
       </c>
       <c r="N38">
-        <v>5.6504192</v>
+        <v>5.6234864</v>
       </c>
       <c r="O38">
-        <v>1.525613184</v>
+        <v>1.518341328</v>
       </c>
       <c r="P38">
-        <v>4.124806016</v>
+        <v>4.105145072</v>
       </c>
       <c r="Q38">
-        <v>5.294806016</v>
+        <v>5.275145072</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1524126488835577</v>
+        <v>0.153781006122852</v>
       </c>
       <c r="T38">
-        <v>1.277192062161109</v>
+        <v>1.293584629295766</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.827692957616323</v>
+        <v>6.643160715518584</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1115484638573968</v>
+        <v>0.1112827924293166</v>
       </c>
       <c r="C39">
-        <v>36.80965318786265</v>
+        <v>36.48714226870402</v>
       </c>
       <c r="D39">
-        <v>42.76165318786265</v>
+        <v>42.93514226870403</v>
       </c>
       <c r="E39">
-        <v>18.352</v>
+        <v>18.848</v>
       </c>
       <c r="F39">
-        <v>18.352</v>
+        <v>18.848</v>
       </c>
       <c r="G39">
         <v>12.4</v>
@@ -4485,28 +4485,28 @@
         <v>6.62</v>
       </c>
       <c r="M39">
-        <v>0.9965136</v>
+        <v>1.0234464</v>
       </c>
       <c r="N39">
-        <v>5.6234864</v>
+        <v>5.5965536</v>
       </c>
       <c r="O39">
-        <v>1.518341328</v>
+        <v>1.511069472</v>
       </c>
       <c r="P39">
-        <v>4.105145072</v>
+        <v>4.085484128</v>
       </c>
       <c r="Q39">
-        <v>5.275145072</v>
+        <v>5.255484128</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.153781006122852</v>
+        <v>0.1551935039182525</v>
       </c>
       <c r="T39">
-        <v>1.293584629295766</v>
+        <v>1.310505988918638</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.643160715518584</v>
+        <v>6.468340696689147</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1112827924293166</v>
+        <v>0.1110171210012364</v>
       </c>
       <c r="C40">
-        <v>36.48714226870402</v>
+        <v>36.1660448155542</v>
       </c>
       <c r="D40">
-        <v>42.93514226870403</v>
+        <v>43.1100448155542</v>
       </c>
       <c r="E40">
-        <v>18.848</v>
+        <v>19.344</v>
       </c>
       <c r="F40">
-        <v>18.848</v>
+        <v>19.344</v>
       </c>
       <c r="G40">
         <v>12.4</v>
@@ -4567,28 +4567,28 @@
         <v>6.62</v>
       </c>
       <c r="M40">
-        <v>1.0234464</v>
+        <v>1.0503792</v>
       </c>
       <c r="N40">
-        <v>5.5965536</v>
+        <v>5.5696208</v>
       </c>
       <c r="O40">
-        <v>1.511069472</v>
+        <v>1.503797616</v>
       </c>
       <c r="P40">
-        <v>4.085484128</v>
+        <v>4.065823184</v>
       </c>
       <c r="Q40">
-        <v>5.255484128</v>
+        <v>5.235823184</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1551935039182525</v>
+        <v>0.156652313116781</v>
       </c>
       <c r="T40">
-        <v>1.310505988918638</v>
+        <v>1.32798214721767</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.468340696689147</v>
+        <v>6.302485807030451</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1110171210012364</v>
+        <v>0.1107514495731562</v>
       </c>
       <c r="C41">
-        <v>36.1660448155542</v>
+        <v>35.84637817294676</v>
       </c>
       <c r="D41">
-        <v>43.1100448155542</v>
+        <v>43.28637817294676</v>
       </c>
       <c r="E41">
-        <v>19.344</v>
+        <v>19.84</v>
       </c>
       <c r="F41">
-        <v>19.344</v>
+        <v>19.84</v>
       </c>
       <c r="G41">
         <v>12.4</v>
@@ -4649,28 +4649,28 @@
         <v>6.62</v>
       </c>
       <c r="M41">
-        <v>1.0503792</v>
+        <v>1.077312</v>
       </c>
       <c r="N41">
-        <v>5.5696208</v>
+        <v>5.542688</v>
       </c>
       <c r="O41">
-        <v>1.503797616</v>
+        <v>1.49652576</v>
       </c>
       <c r="P41">
-        <v>4.065823184</v>
+        <v>4.04616224</v>
       </c>
       <c r="Q41">
-        <v>5.235823184</v>
+        <v>5.21616224</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.156652313116781</v>
+        <v>0.1581597492885937</v>
       </c>
       <c r="T41">
-        <v>1.32798214721767</v>
+        <v>1.346040844126669</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.302485807030451</v>
+        <v>6.144923661854689</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1107514495731562</v>
+        <v>0.110785078145076</v>
       </c>
       <c r="C42">
-        <v>35.84637817294676</v>
+        <v>35.32797827556897</v>
       </c>
       <c r="D42">
-        <v>43.28637817294676</v>
+        <v>43.26397827556897</v>
       </c>
       <c r="E42">
-        <v>19.84</v>
+        <v>20.336</v>
       </c>
       <c r="F42">
-        <v>19.84</v>
+        <v>20.336</v>
       </c>
       <c r="G42">
         <v>12.4</v>
@@ -4731,45 +4731,45 @@
         <v>6.62</v>
       </c>
       <c r="M42">
-        <v>1.077312</v>
+        <v>1.1245808</v>
       </c>
       <c r="N42">
-        <v>5.542688</v>
+        <v>5.4954192</v>
       </c>
       <c r="O42">
-        <v>1.49652576</v>
+        <v>1.483763184</v>
       </c>
       <c r="P42">
-        <v>4.04616224</v>
+        <v>4.011656016</v>
       </c>
       <c r="Q42">
-        <v>5.21616224</v>
+        <v>5.181656016</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1581597492885937</v>
+        <v>0.1597182849916543</v>
       </c>
       <c r="T42">
-        <v>1.346040844126669</v>
+        <v>1.364711700252922</v>
       </c>
       <c r="U42">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V42">
         <v>0.27</v>
       </c>
       <c r="W42">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>6.144923661854689</v>
+        <v>5.88663793655378</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.110785078145076</v>
+        <v>0.1105267067169959</v>
       </c>
       <c r="C43">
-        <v>35.32797827556897</v>
+        <v>35.00467632276552</v>
       </c>
       <c r="D43">
-        <v>43.26397827556897</v>
+        <v>43.43667632276553</v>
       </c>
       <c r="E43">
-        <v>20.336</v>
+        <v>20.832</v>
       </c>
       <c r="F43">
-        <v>20.336</v>
+        <v>20.832</v>
       </c>
       <c r="G43">
         <v>12.4</v>
@@ -4813,28 +4813,28 @@
         <v>6.62</v>
       </c>
       <c r="M43">
-        <v>1.1245808</v>
+        <v>1.1520096</v>
       </c>
       <c r="N43">
-        <v>5.4954192</v>
+        <v>5.4679904</v>
       </c>
       <c r="O43">
-        <v>1.483763184</v>
+        <v>1.476357408</v>
       </c>
       <c r="P43">
-        <v>4.011656016</v>
+        <v>3.991632992</v>
       </c>
       <c r="Q43">
-        <v>5.181656016</v>
+        <v>5.161632991999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1597182849916543</v>
+        <v>0.1613305633051653</v>
       </c>
       <c r="T43">
-        <v>1.364711700252922</v>
+        <v>1.384026379004219</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.88663793655378</v>
+        <v>5.746479890445356</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1105267067169959</v>
+        <v>0.1102683352889157</v>
       </c>
       <c r="C44">
-        <v>35.00467632276553</v>
+        <v>34.68275862289431</v>
       </c>
       <c r="D44">
-        <v>43.43667632276553</v>
+        <v>43.61075862289432</v>
       </c>
       <c r="E44">
-        <v>20.832</v>
+        <v>21.328</v>
       </c>
       <c r="F44">
-        <v>20.832</v>
+        <v>21.328</v>
       </c>
       <c r="G44">
         <v>12.4</v>
@@ -4895,28 +4895,28 @@
         <v>6.62</v>
       </c>
       <c r="M44">
-        <v>1.1520096</v>
+        <v>1.1794384</v>
       </c>
       <c r="N44">
-        <v>5.4679904</v>
+        <v>5.440561600000001</v>
       </c>
       <c r="O44">
-        <v>1.476357408</v>
+        <v>1.468951632</v>
       </c>
       <c r="P44">
-        <v>3.991632992</v>
+        <v>3.971609968</v>
       </c>
       <c r="Q44">
-        <v>5.161632991999999</v>
+        <v>5.141609968</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1613305633051653</v>
+        <v>0.1629994127875714</v>
       </c>
       <c r="T44">
-        <v>1.384026379004219</v>
+        <v>1.404018765781877</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.746479890445356</v>
+        <v>5.612840823225699</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1102683352889157</v>
+        <v>0.1100099638608355</v>
       </c>
       <c r="C45">
-        <v>34.68275862289431</v>
+        <v>34.36224188604454</v>
       </c>
       <c r="D45">
-        <v>43.61075862289432</v>
+        <v>43.78624188604455</v>
       </c>
       <c r="E45">
-        <v>21.328</v>
+        <v>21.824</v>
       </c>
       <c r="F45">
-        <v>21.328</v>
+        <v>21.824</v>
       </c>
       <c r="G45">
         <v>12.4</v>
@@ -4977,28 +4977,28 @@
         <v>6.62</v>
       </c>
       <c r="M45">
-        <v>1.1794384</v>
+        <v>1.2068672</v>
       </c>
       <c r="N45">
-        <v>5.440561600000001</v>
+        <v>5.4131328</v>
       </c>
       <c r="O45">
-        <v>1.468951632</v>
+        <v>1.461545856</v>
       </c>
       <c r="P45">
-        <v>3.971609968</v>
+        <v>3.951586944</v>
       </c>
       <c r="Q45">
-        <v>5.141609968</v>
+        <v>5.121586944</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1629994127875714</v>
+        <v>0.1647278640372062</v>
       </c>
       <c r="T45">
-        <v>1.404018765781877</v>
+        <v>1.424725166373022</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.612840823225699</v>
+        <v>5.485276259061477</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1100099638608355</v>
+        <v>0.1097515924327553</v>
       </c>
       <c r="C46">
-        <v>34.36224188604454</v>
+        <v>34.04314309234769</v>
       </c>
       <c r="D46">
-        <v>43.78624188604455</v>
+        <v>43.96314309234769</v>
       </c>
       <c r="E46">
-        <v>21.824</v>
+        <v>22.32</v>
       </c>
       <c r="F46">
-        <v>21.824</v>
+        <v>22.32</v>
       </c>
       <c r="G46">
         <v>12.4</v>
@@ -5059,28 +5059,28 @@
         <v>6.62</v>
       </c>
       <c r="M46">
-        <v>1.2068672</v>
+        <v>1.234296</v>
       </c>
       <c r="N46">
-        <v>5.4131328</v>
+        <v>5.385704</v>
       </c>
       <c r="O46">
-        <v>1.461545856</v>
+        <v>1.45414008</v>
       </c>
       <c r="P46">
-        <v>3.951586944</v>
+        <v>3.93156392</v>
       </c>
       <c r="Q46">
-        <v>5.121586944</v>
+        <v>5.10156392</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1647278640372062</v>
+        <v>0.1665191680595551</v>
       </c>
       <c r="T46">
-        <v>1.424725166373022</v>
+        <v>1.446184526985665</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.485276259061477</v>
+        <v>5.363381231082334</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1097515924327553</v>
+        <v>0.1094932210046751</v>
       </c>
       <c r="C47">
-        <v>34.04314309234769</v>
+        <v>33.72547949745474</v>
       </c>
       <c r="D47">
-        <v>43.96314309234769</v>
+        <v>44.14147949745475</v>
       </c>
       <c r="E47">
-        <v>22.32</v>
+        <v>22.816</v>
       </c>
       <c r="F47">
-        <v>22.32</v>
+        <v>22.816</v>
       </c>
       <c r="G47">
         <v>12.4</v>
@@ -5141,28 +5141,28 @@
         <v>6.62</v>
       </c>
       <c r="M47">
-        <v>1.234296</v>
+        <v>1.2617248</v>
       </c>
       <c r="N47">
-        <v>5.385704</v>
+        <v>5.3582752</v>
       </c>
       <c r="O47">
-        <v>1.45414008</v>
+        <v>1.446734304</v>
       </c>
       <c r="P47">
-        <v>3.93156392</v>
+        <v>3.911540896</v>
       </c>
       <c r="Q47">
-        <v>5.10156392</v>
+        <v>5.081540896</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1665191680595551</v>
+        <v>0.1683768166753243</v>
       </c>
       <c r="T47">
-        <v>1.446184526985665</v>
+        <v>1.468438678732108</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.363381231082334</v>
+        <v>5.246785986928369</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1094932210046751</v>
+        <v>0.1092348495765949</v>
       </c>
       <c r="C48">
-        <v>33.72547949745474</v>
+        <v>33.40926863814718</v>
       </c>
       <c r="D48">
-        <v>44.14147949745475</v>
+        <v>44.32126863814719</v>
       </c>
       <c r="E48">
-        <v>22.816</v>
+        <v>23.312</v>
       </c>
       <c r="F48">
-        <v>22.816</v>
+        <v>23.312</v>
       </c>
       <c r="G48">
         <v>12.4</v>
@@ -5223,28 +5223,28 @@
         <v>6.62</v>
       </c>
       <c r="M48">
-        <v>1.2617248</v>
+        <v>1.2891536</v>
       </c>
       <c r="N48">
-        <v>5.3582752</v>
+        <v>5.3308464</v>
       </c>
       <c r="O48">
-        <v>1.446734304</v>
+        <v>1.439328528</v>
       </c>
       <c r="P48">
-        <v>3.911540896</v>
+        <v>3.891517872000001</v>
       </c>
       <c r="Q48">
-        <v>5.081540896</v>
+        <v>5.061517872</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1683768166753243</v>
+        <v>0.1703045652388584</v>
       </c>
       <c r="T48">
-        <v>1.468438678732108</v>
+        <v>1.491532609789738</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.246785986928369</v>
+        <v>5.135152242525638</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1092348495765949</v>
+        <v>0.1089764781485148</v>
       </c>
       <c r="C49">
-        <v>33.40926863814718</v>
+        <v>33.09452833808555</v>
       </c>
       <c r="D49">
-        <v>44.32126863814719</v>
+        <v>44.50252833808556</v>
       </c>
       <c r="E49">
-        <v>23.312</v>
+        <v>23.808</v>
       </c>
       <c r="F49">
-        <v>23.312</v>
+        <v>23.808</v>
       </c>
       <c r="G49">
         <v>12.4</v>
@@ -5305,28 +5305,28 @@
         <v>6.62</v>
       </c>
       <c r="M49">
-        <v>1.2891536</v>
+        <v>1.3165824</v>
       </c>
       <c r="N49">
-        <v>5.3308464</v>
+        <v>5.3034176</v>
       </c>
       <c r="O49">
-        <v>1.439328528</v>
+        <v>1.431922752</v>
       </c>
       <c r="P49">
-        <v>3.891517872000001</v>
+        <v>3.871494847999999</v>
       </c>
       <c r="Q49">
-        <v>5.061517872</v>
+        <v>5.041494847999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1703045652388584</v>
+        <v>0.172306457977913</v>
       </c>
       <c r="T49">
-        <v>1.491532609789738</v>
+        <v>1.51551476896497</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.135152242525638</v>
+        <v>5.028169904139687</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1089764781485148</v>
+        <v>0.1087181067204346</v>
       </c>
       <c r="C50">
-        <v>33.09452833808556</v>
+        <v>32.78127671369992</v>
       </c>
       <c r="D50">
-        <v>44.50252833808556</v>
+        <v>44.68527671369992</v>
       </c>
       <c r="E50">
-        <v>23.808</v>
+        <v>24.304</v>
       </c>
       <c r="F50">
-        <v>23.808</v>
+        <v>24.304</v>
       </c>
       <c r="G50">
         <v>12.4</v>
@@ -5387,28 +5387,28 @@
         <v>6.62</v>
       </c>
       <c r="M50">
-        <v>1.3165824</v>
+        <v>1.3440112</v>
       </c>
       <c r="N50">
-        <v>5.3034176</v>
+        <v>5.2759888</v>
       </c>
       <c r="O50">
-        <v>1.431922752</v>
+        <v>1.424516976</v>
       </c>
       <c r="P50">
-        <v>3.871494848</v>
+        <v>3.851471824</v>
       </c>
       <c r="Q50">
-        <v>5.041494848</v>
+        <v>5.021471824</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.172306457977913</v>
+        <v>0.1743868563145776</v>
       </c>
       <c r="T50">
-        <v>1.51551476896497</v>
+        <v>1.540437404970602</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.028169904139689</v>
+        <v>4.925554191810306</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1087181067204346</v>
+        <v>0.1084597352923544</v>
       </c>
       <c r="C51">
-        <v>32.78127671369992</v>
+        <v>32.46953218022573</v>
       </c>
       <c r="D51">
-        <v>44.68527671369992</v>
+        <v>44.86953218022573</v>
       </c>
       <c r="E51">
-        <v>24.304</v>
+        <v>24.8</v>
       </c>
       <c r="F51">
-        <v>24.304</v>
+        <v>24.8</v>
       </c>
       <c r="G51">
         <v>12.4</v>
@@ -5469,28 +5469,28 @@
         <v>6.62</v>
       </c>
       <c r="M51">
-        <v>1.3440112</v>
+        <v>1.37144</v>
       </c>
       <c r="N51">
-        <v>5.2759888</v>
+        <v>5.24856</v>
       </c>
       <c r="O51">
-        <v>1.424516976</v>
+        <v>1.4171112</v>
       </c>
       <c r="P51">
-        <v>3.851471824</v>
+        <v>3.8314488</v>
       </c>
       <c r="Q51">
-        <v>5.021471824</v>
+        <v>5.0014488</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1743868563145776</v>
+        <v>0.1765504705847088</v>
       </c>
       <c r="T51">
-        <v>1.540437404970602</v>
+        <v>1.56635694641646</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.925554191810306</v>
+        <v>4.827043107974101</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1084597352923544</v>
+        <v>0.1082013638642742</v>
       </c>
       <c r="C52">
-        <v>32.46953218022573</v>
+        <v>32.15931345788992</v>
       </c>
       <c r="D52">
-        <v>44.86953218022573</v>
+        <v>45.05531345788993</v>
       </c>
       <c r="E52">
-        <v>24.8</v>
+        <v>25.296</v>
       </c>
       <c r="F52">
-        <v>24.8</v>
+        <v>25.296</v>
       </c>
       <c r="G52">
         <v>12.4</v>
@@ -5551,28 +5551,28 @@
         <v>6.62</v>
       </c>
       <c r="M52">
-        <v>1.37144</v>
+        <v>1.3988688</v>
       </c>
       <c r="N52">
-        <v>5.24856</v>
+        <v>5.2211312</v>
       </c>
       <c r="O52">
-        <v>1.4171112</v>
+        <v>1.409705424</v>
       </c>
       <c r="P52">
-        <v>3.8314488</v>
+        <v>3.811425776</v>
       </c>
       <c r="Q52">
-        <v>5.0014488</v>
+        <v>4.981425776</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1765504705847088</v>
+        <v>0.178802395641376</v>
       </c>
       <c r="T52">
-        <v>1.56635694641646</v>
+        <v>1.593334428329496</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.827043107974101</v>
+        <v>4.732395203896177</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1082013638642742</v>
+        <v>0.1079429924361941</v>
       </c>
       <c r="C53">
-        <v>32.15931345788992</v>
+        <v>31.85063957825126</v>
       </c>
       <c r="D53">
-        <v>45.05531345788993</v>
+        <v>45.24263957825126</v>
       </c>
       <c r="E53">
-        <v>25.296</v>
+        <v>25.792</v>
       </c>
       <c r="F53">
-        <v>25.296</v>
+        <v>25.792</v>
       </c>
       <c r="G53">
         <v>12.4</v>
@@ -5633,28 +5633,28 @@
         <v>6.62</v>
       </c>
       <c r="M53">
-        <v>1.3988688</v>
+        <v>1.4262976</v>
       </c>
       <c r="N53">
-        <v>5.2211312</v>
+        <v>5.1937024</v>
       </c>
       <c r="O53">
-        <v>1.409705424</v>
+        <v>1.402299648</v>
       </c>
       <c r="P53">
-        <v>3.811425776</v>
+        <v>3.791402752</v>
       </c>
       <c r="Q53">
-        <v>4.981425776</v>
+        <v>4.961402752</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.178802395641376</v>
+        <v>0.1811481509087376</v>
       </c>
       <c r="T53">
-        <v>1.593334428329496</v>
+        <v>1.621435971988908</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.732395203896177</v>
+        <v>4.641387603821251</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1079429924361941</v>
+        <v>0.1076846210081139</v>
       </c>
       <c r="C54">
-        <v>31.85063957825126</v>
+        <v>31.54352989069927</v>
       </c>
       <c r="D54">
-        <v>45.24263957825126</v>
+        <v>45.43152989069927</v>
       </c>
       <c r="E54">
-        <v>25.792</v>
+        <v>26.288</v>
       </c>
       <c r="F54">
-        <v>25.792</v>
+        <v>26.288</v>
       </c>
       <c r="G54">
         <v>12.4</v>
@@ -5715,28 +5715,28 @@
         <v>6.62</v>
       </c>
       <c r="M54">
-        <v>1.4262976</v>
+        <v>1.4537264</v>
       </c>
       <c r="N54">
-        <v>5.1937024</v>
+        <v>5.1662736</v>
       </c>
       <c r="O54">
-        <v>1.402299648</v>
+        <v>1.394893872</v>
       </c>
       <c r="P54">
-        <v>3.791402752</v>
+        <v>3.771379728</v>
       </c>
       <c r="Q54">
-        <v>4.961402752</v>
+        <v>4.941379728</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1811481509087376</v>
+        <v>0.1835937255491785</v>
       </c>
       <c r="T54">
-        <v>1.621435971988908</v>
+        <v>1.650733326016806</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.641387603821251</v>
+        <v>4.553814252805754</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1076846210081139</v>
+        <v>0.1084117495800337</v>
       </c>
       <c r="C55">
-        <v>31.54352989069927</v>
+        <v>30.51992023802011</v>
       </c>
       <c r="D55">
-        <v>45.43152989069927</v>
+        <v>44.90392023802011</v>
       </c>
       <c r="E55">
-        <v>26.288</v>
+        <v>26.784</v>
       </c>
       <c r="F55">
-        <v>26.288</v>
+        <v>26.784</v>
       </c>
       <c r="G55">
         <v>12.4</v>
@@ -5797,45 +5797,45 @@
         <v>6.62</v>
       </c>
       <c r="M55">
-        <v>1.4537264</v>
+        <v>1.5481152</v>
       </c>
       <c r="N55">
-        <v>5.1662736</v>
+        <v>5.071884799999999</v>
       </c>
       <c r="O55">
-        <v>1.394893872</v>
+        <v>1.369408896</v>
       </c>
       <c r="P55">
-        <v>3.771379728</v>
+        <v>3.702475903999999</v>
       </c>
       <c r="Q55">
-        <v>4.941379728</v>
+        <v>4.872475904</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1835937255491785</v>
+        <v>0.1861456295218124</v>
       </c>
       <c r="T55">
-        <v>1.650733326016806</v>
+        <v>1.681304478045916</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.27</v>
       </c>
       <c r="W55">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.553814252805754</v>
+        <v>4.276167561690499</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1084117495800337</v>
+        <v>0.1081716281519535</v>
       </c>
       <c r="C56">
-        <v>30.51992023802011</v>
+        <v>30.19679360646388</v>
       </c>
       <c r="D56">
-        <v>44.90392023802011</v>
+        <v>45.07679360646389</v>
       </c>
       <c r="E56">
-        <v>26.784</v>
+        <v>27.28</v>
       </c>
       <c r="F56">
-        <v>26.784</v>
+        <v>27.28</v>
       </c>
       <c r="G56">
         <v>12.4</v>
@@ -5879,28 +5879,28 @@
         <v>6.62</v>
       </c>
       <c r="M56">
-        <v>1.5481152</v>
+        <v>1.576784</v>
       </c>
       <c r="N56">
-        <v>5.071884799999999</v>
+        <v>5.043215999999999</v>
       </c>
       <c r="O56">
-        <v>1.369408896</v>
+        <v>1.36166832</v>
       </c>
       <c r="P56">
-        <v>3.702475903999999</v>
+        <v>3.68154768</v>
       </c>
       <c r="Q56">
-        <v>4.872475904</v>
+        <v>4.851547679999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1861456295218124</v>
+        <v>0.1888109514487856</v>
       </c>
       <c r="T56">
-        <v>1.681304478045916</v>
+        <v>1.713234347942987</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.276167561690499</v>
+        <v>4.198419060568853</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1081716281519535</v>
+        <v>0.1079315067238733</v>
       </c>
       <c r="C57">
-        <v>30.19679360646388</v>
+        <v>29.87500319230517</v>
       </c>
       <c r="D57">
-        <v>45.07679360646389</v>
+        <v>45.25100319230517</v>
       </c>
       <c r="E57">
-        <v>27.28</v>
+        <v>27.776</v>
       </c>
       <c r="F57">
-        <v>27.28</v>
+        <v>27.776</v>
       </c>
       <c r="G57">
         <v>12.4</v>
@@ -5961,28 +5961,28 @@
         <v>6.62</v>
       </c>
       <c r="M57">
-        <v>1.576784</v>
+        <v>1.6054528</v>
       </c>
       <c r="N57">
-        <v>5.043215999999999</v>
+        <v>5.0145472</v>
       </c>
       <c r="O57">
-        <v>1.36166832</v>
+        <v>1.353927744</v>
       </c>
       <c r="P57">
-        <v>3.68154768</v>
+        <v>3.660619456</v>
       </c>
       <c r="Q57">
-        <v>4.851547679999999</v>
+        <v>4.830619456</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1888109514487856</v>
+        <v>0.1915974243724394</v>
       </c>
       <c r="T57">
-        <v>1.713234347942987</v>
+        <v>1.746615575562653</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.198419060568853</v>
+        <v>4.123447291630123</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1079315067238733</v>
+        <v>0.1076913852957931</v>
       </c>
       <c r="C58">
-        <v>29.87500319230517</v>
+        <v>29.55456454800382</v>
       </c>
       <c r="D58">
-        <v>45.25100319230517</v>
+        <v>45.42656454800382</v>
       </c>
       <c r="E58">
-        <v>27.776</v>
+        <v>28.27200000000001</v>
       </c>
       <c r="F58">
-        <v>27.776</v>
+        <v>28.27200000000001</v>
       </c>
       <c r="G58">
         <v>12.4</v>
@@ -6043,28 +6043,28 @@
         <v>6.62</v>
       </c>
       <c r="M58">
-        <v>1.6054528</v>
+        <v>1.634121600000001</v>
       </c>
       <c r="N58">
-        <v>5.0145472</v>
+        <v>4.9858784</v>
       </c>
       <c r="O58">
-        <v>1.353927744</v>
+        <v>1.346187168</v>
       </c>
       <c r="P58">
-        <v>3.660619456</v>
+        <v>3.639691232</v>
       </c>
       <c r="Q58">
-        <v>4.830619456</v>
+        <v>4.809691232</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1915974243724394</v>
+        <v>0.1945135006878911</v>
       </c>
       <c r="T58">
-        <v>1.746615575562653</v>
+        <v>1.781549418420442</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.123447291630123</v>
+        <v>4.051106111075208</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1076913852957931</v>
+        <v>0.108933163867713</v>
       </c>
       <c r="C59">
-        <v>29.55456454800382</v>
+        <v>28.16506054795333</v>
       </c>
       <c r="D59">
-        <v>45.42656454800382</v>
+        <v>44.53306054795334</v>
       </c>
       <c r="E59">
-        <v>28.27200000000001</v>
+        <v>28.768</v>
       </c>
       <c r="F59">
-        <v>28.27200000000001</v>
+        <v>28.768</v>
       </c>
       <c r="G59">
         <v>12.4</v>
@@ -6125,45 +6125,45 @@
         <v>6.62</v>
       </c>
       <c r="M59">
-        <v>1.634121600000001</v>
+        <v>1.7634784</v>
       </c>
       <c r="N59">
-        <v>4.9858784</v>
+        <v>4.8565216</v>
       </c>
       <c r="O59">
-        <v>1.346187168</v>
+        <v>1.311260832</v>
       </c>
       <c r="P59">
-        <v>3.639691232</v>
+        <v>3.545260767999999</v>
       </c>
       <c r="Q59">
-        <v>4.809691232</v>
+        <v>4.715260767999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1945135006878911</v>
+        <v>0.197568437780269</v>
       </c>
       <c r="T59">
-        <v>1.781549418420442</v>
+        <v>1.818146777604793</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.27</v>
       </c>
       <c r="W59">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.051106111075208</v>
+        <v>3.753944477006352</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1089331638677129</v>
+        <v>0.1087185924396328</v>
       </c>
       <c r="C60">
-        <v>28.16506054795336</v>
+        <v>27.82093175212441</v>
       </c>
       <c r="D60">
-        <v>44.53306054795336</v>
+        <v>44.68493175212441</v>
       </c>
       <c r="E60">
-        <v>28.768</v>
+        <v>29.264</v>
       </c>
       <c r="F60">
-        <v>28.768</v>
+        <v>29.264</v>
       </c>
       <c r="G60">
         <v>12.4</v>
@@ -6207,28 +6207,28 @@
         <v>6.62</v>
       </c>
       <c r="M60">
-        <v>1.7634784</v>
+        <v>1.7938832</v>
       </c>
       <c r="N60">
-        <v>4.856521600000001</v>
+        <v>4.8261168</v>
       </c>
       <c r="O60">
-        <v>1.311260832</v>
+        <v>1.303051536</v>
       </c>
       <c r="P60">
-        <v>3.545260768</v>
+        <v>3.523065264</v>
       </c>
       <c r="Q60">
-        <v>4.715260768</v>
+        <v>4.693065264</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1975684377802689</v>
+        <v>0.2007723961942263</v>
       </c>
       <c r="T60">
-        <v>1.818146777604792</v>
+        <v>1.856529373822526</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.753944477006353</v>
+        <v>3.690318299429974</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1087185924396328</v>
+        <v>0.1085040210115526</v>
       </c>
       <c r="C61">
-        <v>27.82093175212441</v>
+        <v>27.47784235442778</v>
       </c>
       <c r="D61">
-        <v>44.68493175212441</v>
+        <v>44.83784235442778</v>
       </c>
       <c r="E61">
-        <v>29.264</v>
+        <v>29.76</v>
       </c>
       <c r="F61">
-        <v>29.264</v>
+        <v>29.76</v>
       </c>
       <c r="G61">
         <v>12.4</v>
@@ -6289,28 +6289,28 @@
         <v>6.62</v>
       </c>
       <c r="M61">
-        <v>1.7938832</v>
+        <v>1.824288</v>
       </c>
       <c r="N61">
-        <v>4.8261168</v>
+        <v>4.795712</v>
       </c>
       <c r="O61">
-        <v>1.303051536</v>
+        <v>1.29484224</v>
       </c>
       <c r="P61">
-        <v>3.523065264</v>
+        <v>3.50086976</v>
       </c>
       <c r="Q61">
-        <v>4.693065264</v>
+        <v>4.67086976</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2007723961942263</v>
+        <v>0.2041365525288815</v>
       </c>
       <c r="T61">
-        <v>1.856529373822526</v>
+        <v>1.896831099851146</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.690318299429974</v>
+        <v>3.628812994439475</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1085040210115526</v>
+        <v>0.1082894495834724</v>
       </c>
       <c r="C62">
-        <v>27.47784235442778</v>
+        <v>27.13580306187762</v>
       </c>
       <c r="D62">
-        <v>44.83784235442778</v>
+        <v>44.99180306187763</v>
       </c>
       <c r="E62">
-        <v>29.76</v>
+        <v>30.256</v>
       </c>
       <c r="F62">
-        <v>29.76</v>
+        <v>30.256</v>
       </c>
       <c r="G62">
         <v>12.4</v>
@@ -6371,28 +6371,28 @@
         <v>6.62</v>
       </c>
       <c r="M62">
-        <v>1.824288</v>
+        <v>1.8546928</v>
       </c>
       <c r="N62">
-        <v>4.795712</v>
+        <v>4.765307200000001</v>
       </c>
       <c r="O62">
-        <v>1.29484224</v>
+        <v>1.286632944</v>
       </c>
       <c r="P62">
-        <v>3.50086976</v>
+        <v>3.478674256000001</v>
       </c>
       <c r="Q62">
-        <v>4.67086976</v>
+        <v>4.648674256000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2041365525288815</v>
+        <v>0.2076732297012113</v>
       </c>
       <c r="T62">
-        <v>1.896831099851146</v>
+        <v>1.939199581060722</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.628812994439475</v>
+        <v>3.569324256825713</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1082894495834724</v>
+        <v>0.1080748781553922</v>
       </c>
       <c r="C63">
-        <v>27.13580306187762</v>
+        <v>26.79482472905456</v>
       </c>
       <c r="D63">
-        <v>44.99180306187763</v>
+        <v>45.14682472905456</v>
       </c>
       <c r="E63">
-        <v>30.256</v>
+        <v>30.752</v>
       </c>
       <c r="F63">
-        <v>30.256</v>
+        <v>30.752</v>
       </c>
       <c r="G63">
         <v>12.4</v>
@@ -6453,28 +6453,28 @@
         <v>6.62</v>
       </c>
       <c r="M63">
-        <v>1.8546928</v>
+        <v>1.8850976</v>
       </c>
       <c r="N63">
-        <v>4.765307200000001</v>
+        <v>4.7349024</v>
       </c>
       <c r="O63">
-        <v>1.286632944</v>
+        <v>1.278423648</v>
       </c>
       <c r="P63">
-        <v>3.478674256000001</v>
+        <v>3.456478752</v>
       </c>
       <c r="Q63">
-        <v>4.648674256000001</v>
+        <v>4.626478752</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2076732297012113</v>
+        <v>0.211396047777348</v>
       </c>
       <c r="T63">
-        <v>1.939199581060722</v>
+        <v>1.983797982333959</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.569324256825713</v>
+        <v>3.511754510747879</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1080748781553922</v>
+        <v>0.1091480267273121</v>
       </c>
       <c r="C64">
-        <v>26.79482472905456</v>
+        <v>25.5340140003281</v>
       </c>
       <c r="D64">
-        <v>45.14682472905456</v>
+        <v>44.3820140003281</v>
       </c>
       <c r="E64">
-        <v>30.752</v>
+        <v>31.248</v>
       </c>
       <c r="F64">
-        <v>30.752</v>
+        <v>31.248</v>
       </c>
       <c r="G64">
         <v>12.4</v>
@@ -6535,45 +6535,45 @@
         <v>6.62</v>
       </c>
       <c r="M64">
-        <v>1.8850976</v>
+        <v>2.0029968</v>
       </c>
       <c r="N64">
-        <v>4.7349024</v>
+        <v>4.6170032</v>
       </c>
       <c r="O64">
-        <v>1.278423648</v>
+        <v>1.246590864</v>
       </c>
       <c r="P64">
-        <v>3.456478752</v>
+        <v>3.370412336</v>
       </c>
       <c r="Q64">
-        <v>4.626478752</v>
+        <v>4.540412336</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.211396047777348</v>
+        <v>0.2153200992630055</v>
       </c>
       <c r="T64">
-        <v>1.983797982333959</v>
+        <v>2.030807108000344</v>
       </c>
       <c r="U64">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V64">
         <v>0.27</v>
       </c>
       <c r="W64">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y64">
-        <v>3.511754510747879</v>
+        <v>3.305047716501594</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1091480267273121</v>
+        <v>0.1089538952992319</v>
       </c>
       <c r="C65">
-        <v>25.5340140003281</v>
+        <v>25.17444174905419</v>
       </c>
       <c r="D65">
-        <v>44.3820140003281</v>
+        <v>44.51844174905419</v>
       </c>
       <c r="E65">
-        <v>31.248</v>
+        <v>31.744</v>
       </c>
       <c r="F65">
-        <v>31.248</v>
+        <v>31.744</v>
       </c>
       <c r="G65">
         <v>12.4</v>
@@ -6617,28 +6617,28 @@
         <v>6.62</v>
       </c>
       <c r="M65">
-        <v>2.0029968</v>
+        <v>2.0347904</v>
       </c>
       <c r="N65">
-        <v>4.6170032</v>
+        <v>4.5852096</v>
       </c>
       <c r="O65">
-        <v>1.246590864</v>
+        <v>1.238006592</v>
       </c>
       <c r="P65">
-        <v>3.370412336</v>
+        <v>3.347203008</v>
       </c>
       <c r="Q65">
-        <v>4.540412336</v>
+        <v>4.517203007999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2153200992630055</v>
+        <v>0.2194621536089774</v>
       </c>
       <c r="T65">
-        <v>2.030807108000344</v>
+        <v>2.080427851759306</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.305047716501594</v>
+        <v>3.253406345931256</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1089538952992319</v>
+        <v>0.1087597638711517</v>
       </c>
       <c r="C66">
-        <v>25.17444174905419</v>
+        <v>24.81571082602112</v>
       </c>
       <c r="D66">
-        <v>44.51844174905419</v>
+        <v>44.65571082602112</v>
       </c>
       <c r="E66">
-        <v>31.744</v>
+        <v>32.24</v>
       </c>
       <c r="F66">
-        <v>31.744</v>
+        <v>32.24</v>
       </c>
       <c r="G66">
         <v>12.4</v>
@@ -6699,28 +6699,28 @@
         <v>6.62</v>
       </c>
       <c r="M66">
-        <v>2.0347904</v>
+        <v>2.066584</v>
       </c>
       <c r="N66">
-        <v>4.5852096</v>
+        <v>4.553416</v>
       </c>
       <c r="O66">
-        <v>1.238006592</v>
+        <v>1.22942232</v>
       </c>
       <c r="P66">
-        <v>3.347203008</v>
+        <v>3.32399368</v>
       </c>
       <c r="Q66">
-        <v>4.517203007999999</v>
+        <v>4.49399368</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2194621536089774</v>
+        <v>0.2238408967747191</v>
       </c>
       <c r="T66">
-        <v>2.080427851759306</v>
+        <v>2.132884066590209</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.253406345931256</v>
+        <v>3.203353940609237</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1087597638711517</v>
+        <v>0.1085656324430715</v>
       </c>
       <c r="C67">
-        <v>24.81571082602112</v>
+        <v>24.45782903780611</v>
       </c>
       <c r="D67">
-        <v>44.65571082602112</v>
+        <v>44.79382903780612</v>
       </c>
       <c r="E67">
-        <v>32.24</v>
+        <v>32.736</v>
       </c>
       <c r="F67">
-        <v>32.24</v>
+        <v>32.736</v>
       </c>
       <c r="G67">
         <v>12.4</v>
@@ -6781,28 +6781,28 @@
         <v>6.62</v>
       </c>
       <c r="M67">
-        <v>2.066584</v>
+        <v>2.098377600000001</v>
       </c>
       <c r="N67">
-        <v>4.553416</v>
+        <v>4.5216224</v>
       </c>
       <c r="O67">
-        <v>1.22942232</v>
+        <v>1.220838048</v>
       </c>
       <c r="P67">
-        <v>3.32399368</v>
+        <v>3.300784352</v>
       </c>
       <c r="Q67">
-        <v>4.49399368</v>
+        <v>4.470784352</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2238408967747191</v>
+        <v>0.2284772130678573</v>
       </c>
       <c r="T67">
-        <v>2.132884066590209</v>
+        <v>2.188425941117046</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.203353940609237</v>
+        <v>3.15481827484243</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1085656324430715</v>
+        <v>0.1083715010149913</v>
       </c>
       <c r="C68">
-        <v>24.45782903780611</v>
+        <v>24.10080428786772</v>
       </c>
       <c r="D68">
-        <v>44.79382903780612</v>
+        <v>44.93280428786773</v>
       </c>
       <c r="E68">
-        <v>32.736</v>
+        <v>33.23200000000001</v>
       </c>
       <c r="F68">
-        <v>32.736</v>
+        <v>33.23200000000001</v>
       </c>
       <c r="G68">
         <v>12.4</v>
@@ -6863,28 +6863,28 @@
         <v>6.62</v>
       </c>
       <c r="M68">
-        <v>2.098377600000001</v>
+        <v>2.1301712</v>
       </c>
       <c r="N68">
-        <v>4.5216224</v>
+        <v>4.4898288</v>
       </c>
       <c r="O68">
-        <v>1.220838048</v>
+        <v>1.212253776</v>
       </c>
       <c r="P68">
-        <v>3.300784352</v>
+        <v>3.277575024</v>
       </c>
       <c r="Q68">
-        <v>4.470784352</v>
+        <v>4.447575024</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2284772130678573</v>
+        <v>0.2333945182272465</v>
       </c>
       <c r="T68">
-        <v>2.188425941117046</v>
+        <v>2.247333989857633</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.15481827484243</v>
+        <v>3.107731434919409</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1083715010149913</v>
+        <v>0.1081773695869112</v>
       </c>
       <c r="C69">
-        <v>24.10080428786772</v>
+        <v>23.74464457805337</v>
       </c>
       <c r="D69">
-        <v>44.93280428786773</v>
+        <v>45.07264457805337</v>
       </c>
       <c r="E69">
-        <v>33.23200000000001</v>
+        <v>33.728</v>
       </c>
       <c r="F69">
-        <v>33.23200000000001</v>
+        <v>33.728</v>
       </c>
       <c r="G69">
         <v>12.4</v>
@@ -6945,28 +6945,28 @@
         <v>6.62</v>
       </c>
       <c r="M69">
-        <v>2.1301712</v>
+        <v>2.1619648</v>
       </c>
       <c r="N69">
-        <v>4.4898288</v>
+        <v>4.458035199999999</v>
       </c>
       <c r="O69">
-        <v>1.212253776</v>
+        <v>1.203669504</v>
       </c>
       <c r="P69">
-        <v>3.277575024</v>
+        <v>3.254365696</v>
       </c>
       <c r="Q69">
-        <v>4.447575024</v>
+        <v>4.424365696</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2333945182272465</v>
+        <v>0.2386191549590974</v>
       </c>
       <c r="T69">
-        <v>2.247333989857633</v>
+        <v>2.309923791644505</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.107731434919409</v>
+        <v>3.062029502052947</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1081773695869112</v>
+        <v>0.107983238158831</v>
       </c>
       <c r="C70">
-        <v>23.74464457805337</v>
+        <v>23.38935801013515</v>
       </c>
       <c r="D70">
-        <v>45.07264457805337</v>
+        <v>45.21335801013515</v>
       </c>
       <c r="E70">
-        <v>33.728</v>
+        <v>34.224</v>
       </c>
       <c r="F70">
-        <v>33.728</v>
+        <v>34.224</v>
       </c>
       <c r="G70">
         <v>12.4</v>
@@ -7027,28 +7027,28 @@
         <v>6.62</v>
       </c>
       <c r="M70">
-        <v>2.1619648</v>
+        <v>2.193758400000001</v>
       </c>
       <c r="N70">
-        <v>4.458035199999999</v>
+        <v>4.426241599999999</v>
       </c>
       <c r="O70">
-        <v>1.203669504</v>
+        <v>1.195085232</v>
       </c>
       <c r="P70">
-        <v>3.254365696</v>
+        <v>3.231156367999999</v>
       </c>
       <c r="Q70">
-        <v>4.424365696</v>
+        <v>4.401156367999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2386191549590974</v>
+        <v>0.244180865028487</v>
       </c>
       <c r="T70">
-        <v>2.309923791644505</v>
+        <v>2.376551645159563</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.062029502052947</v>
+        <v>3.017652262892759</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.107983238158831</v>
+        <v>0.1117749067307508</v>
       </c>
       <c r="C71">
-        <v>23.38935801013515</v>
+        <v>20.29488417981015</v>
       </c>
       <c r="D71">
-        <v>45.21335801013515</v>
+        <v>42.61488417981015</v>
       </c>
       <c r="E71">
-        <v>34.224</v>
+        <v>34.72000000000001</v>
       </c>
       <c r="F71">
-        <v>34.224</v>
+        <v>34.72000000000001</v>
       </c>
       <c r="G71">
         <v>12.4</v>
@@ -7109,45 +7109,45 @@
         <v>6.62</v>
       </c>
       <c r="M71">
-        <v>2.193758400000001</v>
+        <v>2.496368000000001</v>
       </c>
       <c r="N71">
-        <v>4.426241599999999</v>
+        <v>4.123631999999999</v>
       </c>
       <c r="O71">
-        <v>1.195085232</v>
+        <v>1.11338064</v>
       </c>
       <c r="P71">
-        <v>3.231156367999999</v>
+        <v>3.010251359999999</v>
       </c>
       <c r="Q71">
-        <v>4.401156367999999</v>
+        <v>4.180251359999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.244180865028487</v>
+        <v>0.2501133557691693</v>
       </c>
       <c r="T71">
-        <v>2.376551645159563</v>
+        <v>2.447621355575625</v>
       </c>
       <c r="U71">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.017652262892759</v>
+        <v>2.651852611473949</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1117749067307508</v>
+        <v>0.1116377153026706</v>
       </c>
       <c r="C72">
-        <v>20.29488417981015</v>
+        <v>19.88768429675257</v>
       </c>
       <c r="D72">
-        <v>42.61488417981015</v>
+        <v>42.70368429675258</v>
       </c>
       <c r="E72">
-        <v>34.72000000000001</v>
+        <v>35.21600000000001</v>
       </c>
       <c r="F72">
-        <v>34.72000000000001</v>
+        <v>35.21600000000001</v>
       </c>
       <c r="G72">
         <v>12.4</v>
@@ -7191,28 +7191,28 @@
         <v>6.62</v>
       </c>
       <c r="M72">
-        <v>2.496368000000001</v>
+        <v>2.532030400000001</v>
       </c>
       <c r="N72">
-        <v>4.123631999999999</v>
+        <v>4.087969599999999</v>
       </c>
       <c r="O72">
-        <v>1.11338064</v>
+        <v>1.103751792</v>
       </c>
       <c r="P72">
-        <v>3.010251359999999</v>
+        <v>2.984217807999999</v>
       </c>
       <c r="Q72">
-        <v>4.180251359999999</v>
+        <v>4.154217807999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2501133557691693</v>
+        <v>0.2564549838023125</v>
       </c>
       <c r="T72">
-        <v>2.447621355575625</v>
+        <v>2.523592425330725</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.651852611473949</v>
+        <v>2.614502574692625</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1116377153026706</v>
+        <v>0.1115005238745904</v>
       </c>
       <c r="C73">
-        <v>19.88768429675258</v>
+        <v>19.48085526659354</v>
       </c>
       <c r="D73">
-        <v>42.70368429675258</v>
+        <v>42.79285526659354</v>
       </c>
       <c r="E73">
-        <v>35.216</v>
+        <v>35.712</v>
       </c>
       <c r="F73">
-        <v>35.216</v>
+        <v>35.712</v>
       </c>
       <c r="G73">
         <v>12.4</v>
@@ -7273,28 +7273,28 @@
         <v>6.62</v>
       </c>
       <c r="M73">
-        <v>2.5320304</v>
+        <v>2.5676928</v>
       </c>
       <c r="N73">
-        <v>4.087969599999999</v>
+        <v>4.0523072</v>
       </c>
       <c r="O73">
-        <v>1.103751792</v>
+        <v>1.094122944</v>
       </c>
       <c r="P73">
-        <v>2.984217807999999</v>
+        <v>2.958184256</v>
       </c>
       <c r="Q73">
-        <v>4.154217807999999</v>
+        <v>4.128184255999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2564549838023124</v>
+        <v>0.2632495852663944</v>
       </c>
       <c r="T73">
-        <v>2.523592425330724</v>
+        <v>2.604990000068332</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.614502574692626</v>
+        <v>2.578190038933006</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1115005238745904</v>
+        <v>0.1113633324465103</v>
       </c>
       <c r="C74">
-        <v>19.48085526659354</v>
+        <v>19.07439941736474</v>
       </c>
       <c r="D74">
-        <v>42.79285526659354</v>
+        <v>42.88239941736474</v>
       </c>
       <c r="E74">
-        <v>35.712</v>
+        <v>36.208</v>
       </c>
       <c r="F74">
-        <v>35.712</v>
+        <v>36.208</v>
       </c>
       <c r="G74">
         <v>12.4</v>
@@ -7355,28 +7355,28 @@
         <v>6.62</v>
       </c>
       <c r="M74">
-        <v>2.5676928</v>
+        <v>2.6033552</v>
       </c>
       <c r="N74">
-        <v>4.0523072</v>
+        <v>4.0166448</v>
       </c>
       <c r="O74">
-        <v>1.094122944</v>
+        <v>1.084494096</v>
       </c>
       <c r="P74">
-        <v>2.958184256</v>
+        <v>2.932150704</v>
       </c>
       <c r="Q74">
-        <v>4.128184255999999</v>
+        <v>4.102150704</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2632495852663944</v>
+        <v>0.2705474905426305</v>
       </c>
       <c r="T74">
-        <v>2.604990000068332</v>
+        <v>2.692417024786503</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.578190038933006</v>
+        <v>2.542872367166801</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1113633324465103</v>
+        <v>0.1112261410184301</v>
       </c>
       <c r="C75">
-        <v>19.07439941736474</v>
+        <v>18.66831909662438</v>
       </c>
       <c r="D75">
-        <v>42.88239941736474</v>
+        <v>42.97231909662438</v>
       </c>
       <c r="E75">
-        <v>36.208</v>
+        <v>36.704</v>
       </c>
       <c r="F75">
-        <v>36.208</v>
+        <v>36.704</v>
       </c>
       <c r="G75">
         <v>12.4</v>
@@ -7437,28 +7437,28 @@
         <v>6.62</v>
       </c>
       <c r="M75">
-        <v>2.6033552</v>
+        <v>2.6390176</v>
       </c>
       <c r="N75">
-        <v>4.0166448</v>
+        <v>3.9809824</v>
       </c>
       <c r="O75">
-        <v>1.084494096</v>
+        <v>1.074865248</v>
       </c>
       <c r="P75">
-        <v>2.932150704</v>
+        <v>2.906117152</v>
       </c>
       <c r="Q75">
-        <v>4.102150704</v>
+        <v>4.076117152</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2705474905426305</v>
+        <v>0.2784067731478079</v>
       </c>
       <c r="T75">
-        <v>2.692417024786503</v>
+        <v>2.786569205252226</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.542872367166801</v>
+        <v>2.508509227069952</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1112261410184301</v>
+        <v>0.1132241995903499</v>
       </c>
       <c r="C76">
-        <v>18.66831909662438</v>
+        <v>16.89887112026052</v>
       </c>
       <c r="D76">
-        <v>42.97231909662438</v>
+        <v>41.69887112026052</v>
       </c>
       <c r="E76">
-        <v>36.704</v>
+        <v>37.2</v>
       </c>
       <c r="F76">
-        <v>36.704</v>
+        <v>37.2</v>
       </c>
       <c r="G76">
         <v>12.4</v>
@@ -7519,45 +7519,45 @@
         <v>6.62</v>
       </c>
       <c r="M76">
-        <v>2.6390176</v>
+        <v>2.81976</v>
       </c>
       <c r="N76">
-        <v>3.9809824</v>
+        <v>3.80024</v>
       </c>
       <c r="O76">
-        <v>1.074865248</v>
+        <v>1.0260648</v>
       </c>
       <c r="P76">
-        <v>2.906117152</v>
+        <v>2.7741752</v>
       </c>
       <c r="Q76">
-        <v>4.076117152</v>
+        <v>3.9441752</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2784067731478079</v>
+        <v>0.2868947983613995</v>
       </c>
       <c r="T76">
-        <v>2.786569205252226</v>
+        <v>2.888253560155206</v>
       </c>
       <c r="U76">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V76">
         <v>0.27</v>
       </c>
       <c r="W76">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.508509227069952</v>
+        <v>2.347717536244219</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1132241995903499</v>
+        <v>0.1131154781622697</v>
       </c>
       <c r="C77">
-        <v>16.89887112026052</v>
+        <v>16.4702190904643</v>
       </c>
       <c r="D77">
-        <v>41.69887112026052</v>
+        <v>41.76621909046431</v>
       </c>
       <c r="E77">
-        <v>37.2</v>
+        <v>37.69600000000001</v>
       </c>
       <c r="F77">
-        <v>37.2</v>
+        <v>37.69600000000001</v>
       </c>
       <c r="G77">
         <v>12.4</v>
@@ -7601,28 +7601,28 @@
         <v>6.62</v>
       </c>
       <c r="M77">
-        <v>2.81976</v>
+        <v>2.857356800000001</v>
       </c>
       <c r="N77">
-        <v>3.80024</v>
+        <v>3.762643199999999</v>
       </c>
       <c r="O77">
-        <v>1.0260648</v>
+        <v>1.015913664</v>
       </c>
       <c r="P77">
-        <v>2.7741752</v>
+        <v>2.746729535999999</v>
       </c>
       <c r="Q77">
-        <v>3.9441752</v>
+        <v>3.916729535999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2868947983613995</v>
+        <v>0.2960901590094571</v>
       </c>
       <c r="T77">
-        <v>2.888253560155206</v>
+        <v>2.998411611300102</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.347717536244219</v>
+        <v>2.316826516030479</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1131154781622697</v>
+        <v>0.1130067567341895</v>
       </c>
       <c r="C78">
-        <v>16.4702190904643</v>
+        <v>16.04178496041077</v>
       </c>
       <c r="D78">
-        <v>41.76621909046431</v>
+        <v>41.83378496041077</v>
       </c>
       <c r="E78">
-        <v>37.69600000000001</v>
+        <v>38.192</v>
       </c>
       <c r="F78">
-        <v>37.69600000000001</v>
+        <v>38.192</v>
       </c>
       <c r="G78">
         <v>12.4</v>
@@ -7683,28 +7683,28 @@
         <v>6.62</v>
       </c>
       <c r="M78">
-        <v>2.857356800000001</v>
+        <v>2.8949536</v>
       </c>
       <c r="N78">
-        <v>3.762643199999999</v>
+        <v>3.7250464</v>
       </c>
       <c r="O78">
-        <v>1.015913664</v>
+        <v>1.005762528</v>
       </c>
       <c r="P78">
-        <v>2.746729535999999</v>
+        <v>2.719283872</v>
       </c>
       <c r="Q78">
-        <v>3.916729535999999</v>
+        <v>3.889283872</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2960901590094571</v>
+        <v>0.3060851162356066</v>
       </c>
       <c r="T78">
-        <v>2.998411611300102</v>
+        <v>3.118148623414119</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.316826516030479</v>
+        <v>2.286737859978135</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1130067567341895</v>
+        <v>0.1128980353061093</v>
       </c>
       <c r="C79">
-        <v>16.04178496041077</v>
+        <v>15.6135697893129</v>
       </c>
       <c r="D79">
-        <v>41.83378496041077</v>
+        <v>41.9015697893129</v>
       </c>
       <c r="E79">
-        <v>38.192</v>
+        <v>38.688</v>
       </c>
       <c r="F79">
-        <v>38.192</v>
+        <v>38.688</v>
       </c>
       <c r="G79">
         <v>12.4</v>
@@ -7765,28 +7765,28 @@
         <v>6.62</v>
       </c>
       <c r="M79">
-        <v>2.8949536</v>
+        <v>2.9325504</v>
       </c>
       <c r="N79">
-        <v>3.7250464</v>
+        <v>3.6874496</v>
       </c>
       <c r="O79">
-        <v>1.005762528</v>
+        <v>0.995611392</v>
       </c>
       <c r="P79">
-        <v>2.719283872</v>
+        <v>2.691838208</v>
       </c>
       <c r="Q79">
-        <v>3.889283872</v>
+        <v>3.861838208</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3060851162356066</v>
+        <v>0.3169887059368606</v>
       </c>
       <c r="T79">
-        <v>3.118148623414119</v>
+        <v>3.248770818447592</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.286737859978135</v>
+        <v>2.257420707927134</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1128980353061093</v>
+        <v>0.1127893138780292</v>
       </c>
       <c r="C80">
-        <v>15.6135697893129</v>
+        <v>15.18557464326006</v>
       </c>
       <c r="D80">
-        <v>41.9015697893129</v>
+        <v>41.96957464326007</v>
       </c>
       <c r="E80">
-        <v>38.688</v>
+        <v>39.184</v>
       </c>
       <c r="F80">
-        <v>38.688</v>
+        <v>39.184</v>
       </c>
       <c r="G80">
         <v>12.4</v>
@@ -7847,28 +7847,28 @@
         <v>6.62</v>
       </c>
       <c r="M80">
-        <v>2.9325504</v>
+        <v>2.9701472</v>
       </c>
       <c r="N80">
-        <v>3.6874496</v>
+        <v>3.6498528</v>
       </c>
       <c r="O80">
-        <v>0.995611392</v>
+        <v>0.985460256</v>
       </c>
       <c r="P80">
-        <v>2.691838208</v>
+        <v>2.664392544</v>
       </c>
       <c r="Q80">
-        <v>3.861838208</v>
+        <v>3.834392544</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3169887059368606</v>
+        <v>0.3289307327525198</v>
       </c>
       <c r="T80">
-        <v>3.248770818447592</v>
+        <v>3.391833222531872</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.257420707927134</v>
+        <v>2.22884576225717</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1127893138780292</v>
+        <v>0.112680592449949</v>
       </c>
       <c r="C81">
-        <v>15.18557464326006</v>
+        <v>14.75780059527369</v>
       </c>
       <c r="D81">
-        <v>41.96957464326007</v>
+        <v>42.03780059527369</v>
       </c>
       <c r="E81">
-        <v>39.184</v>
+        <v>39.68000000000001</v>
       </c>
       <c r="F81">
-        <v>39.184</v>
+        <v>39.68000000000001</v>
       </c>
       <c r="G81">
         <v>12.4</v>
@@ -7929,28 +7929,28 @@
         <v>6.62</v>
       </c>
       <c r="M81">
-        <v>2.9701472</v>
+        <v>3.007744000000001</v>
       </c>
       <c r="N81">
-        <v>3.6498528</v>
+        <v>3.612255999999999</v>
       </c>
       <c r="O81">
-        <v>0.985460256</v>
+        <v>0.9753091199999999</v>
       </c>
       <c r="P81">
-        <v>2.664392544</v>
+        <v>2.63694688</v>
       </c>
       <c r="Q81">
-        <v>3.834392544</v>
+        <v>3.806946879999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3289307327525198</v>
+        <v>0.3420669622497449</v>
       </c>
       <c r="T81">
-        <v>3.391833222531872</v>
+        <v>3.54920186702458</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.22884576225717</v>
+        <v>2.200985190228955</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.112680592449949</v>
+        <v>0.1125718710218688</v>
       </c>
       <c r="C82">
-        <v>14.75780059527369</v>
+        <v>14.33024872536386</v>
       </c>
       <c r="D82">
-        <v>42.03780059527369</v>
+        <v>42.10624872536386</v>
       </c>
       <c r="E82">
-        <v>39.68000000000001</v>
+        <v>40.176</v>
       </c>
       <c r="F82">
-        <v>39.68000000000001</v>
+        <v>40.176</v>
       </c>
       <c r="G82">
         <v>12.4</v>
@@ -8011,28 +8011,28 @@
         <v>6.62</v>
       </c>
       <c r="M82">
-        <v>3.007744000000001</v>
+        <v>3.0453408</v>
       </c>
       <c r="N82">
-        <v>3.612255999999999</v>
+        <v>3.5746592</v>
       </c>
       <c r="O82">
-        <v>0.9753091199999999</v>
+        <v>0.965157984</v>
       </c>
       <c r="P82">
-        <v>2.63694688</v>
+        <v>2.609501216</v>
       </c>
       <c r="Q82">
-        <v>3.806946879999999</v>
+        <v>3.779501216</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3420669622497449</v>
+        <v>0.3565859527466778</v>
       </c>
       <c r="T82">
-        <v>3.54920186702458</v>
+        <v>3.723135631990204</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.200985190228955</v>
+        <v>2.173812533559462</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1125718710218688</v>
+        <v>0.1124631495937886</v>
       </c>
       <c r="C83">
-        <v>14.33024872536386</v>
+        <v>13.90292012058619</v>
       </c>
       <c r="D83">
-        <v>42.10624872536386</v>
+        <v>42.17492012058619</v>
       </c>
       <c r="E83">
-        <v>40.176</v>
+        <v>40.672</v>
       </c>
       <c r="F83">
-        <v>40.176</v>
+        <v>40.672</v>
       </c>
       <c r="G83">
         <v>12.4</v>
@@ -8093,28 +8093,28 @@
         <v>6.62</v>
       </c>
       <c r="M83">
-        <v>3.0453408</v>
+        <v>3.082937600000001</v>
       </c>
       <c r="N83">
-        <v>3.5746592</v>
+        <v>3.537062399999999</v>
       </c>
       <c r="O83">
-        <v>0.965157984</v>
+        <v>0.9550068479999999</v>
       </c>
       <c r="P83">
-        <v>2.609501216</v>
+        <v>2.582055551999999</v>
       </c>
       <c r="Q83">
-        <v>3.779501216</v>
+        <v>3.752055551999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3565859527466778</v>
+        <v>0.3727181644099368</v>
       </c>
       <c r="T83">
-        <v>3.723135631990204</v>
+        <v>3.916395370840899</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.173812533559462</v>
+        <v>2.147302624613615</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1124631495937886</v>
+        <v>0.1123544281657084</v>
       </c>
       <c r="C84">
-        <v>13.90292012058619</v>
+        <v>13.47581587509948</v>
       </c>
       <c r="D84">
-        <v>42.17492012058619</v>
+        <v>42.24381587509949</v>
       </c>
       <c r="E84">
-        <v>40.672</v>
+        <v>41.16800000000001</v>
       </c>
       <c r="F84">
-        <v>40.672</v>
+        <v>41.16800000000001</v>
       </c>
       <c r="G84">
         <v>12.4</v>
@@ -8175,28 +8175,28 @@
         <v>6.62</v>
       </c>
       <c r="M84">
-        <v>3.082937600000001</v>
+        <v>3.120534400000001</v>
       </c>
       <c r="N84">
-        <v>3.537062399999999</v>
+        <v>3.499465599999999</v>
       </c>
       <c r="O84">
-        <v>0.9550068479999999</v>
+        <v>0.9448557119999998</v>
       </c>
       <c r="P84">
-        <v>2.582055551999999</v>
+        <v>2.554609887999999</v>
       </c>
       <c r="Q84">
-        <v>3.752055551999999</v>
+        <v>3.724609887999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3727181644099368</v>
+        <v>0.3907482833276967</v>
       </c>
       <c r="T84">
-        <v>3.916395370840899</v>
+        <v>4.132391549556381</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.147302624613615</v>
+        <v>2.121431508654415</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1123544281657084</v>
+        <v>0.1122457067376283</v>
       </c>
       <c r="C85">
-        <v>13.47581587509948</v>
+        <v>13.04893709022376</v>
       </c>
       <c r="D85">
-        <v>42.24381587509949</v>
+        <v>42.31293709022377</v>
       </c>
       <c r="E85">
-        <v>41.16800000000001</v>
+        <v>41.66400000000001</v>
       </c>
       <c r="F85">
-        <v>41.16800000000001</v>
+        <v>41.66400000000001</v>
       </c>
       <c r="G85">
         <v>12.4</v>
@@ -8257,28 +8257,28 @@
         <v>6.62</v>
       </c>
       <c r="M85">
-        <v>3.120534400000001</v>
+        <v>3.158131200000001</v>
       </c>
       <c r="N85">
-        <v>3.499465599999999</v>
+        <v>3.461868799999999</v>
       </c>
       <c r="O85">
-        <v>0.9448557119999998</v>
+        <v>0.9347045759999998</v>
       </c>
       <c r="P85">
-        <v>2.554609887999999</v>
+        <v>2.527164223999999</v>
       </c>
       <c r="Q85">
-        <v>3.724609887999999</v>
+        <v>3.697164223999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3907482833276967</v>
+        <v>0.4110321671101768</v>
       </c>
       <c r="T85">
-        <v>4.132391549556381</v>
+        <v>4.375387250611299</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.121431508654415</v>
+        <v>2.096176371646624</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1122457067376283</v>
+        <v>0.112136985309548</v>
       </c>
       <c r="C86">
-        <v>13.04893709022376</v>
+        <v>12.62228487449902</v>
       </c>
       <c r="D86">
-        <v>42.31293709022376</v>
+        <v>42.38228487449902</v>
       </c>
       <c r="E86">
-        <v>41.664</v>
+        <v>42.16</v>
       </c>
       <c r="F86">
-        <v>41.664</v>
+        <v>42.16</v>
       </c>
       <c r="G86">
         <v>12.4</v>
@@ -8339,28 +8339,28 @@
         <v>6.62</v>
       </c>
       <c r="M86">
-        <v>3.158131200000001</v>
+        <v>3.195728</v>
       </c>
       <c r="N86">
-        <v>3.4618688</v>
+        <v>3.424272</v>
       </c>
       <c r="O86">
-        <v>0.9347045759999999</v>
+        <v>0.9245534400000002</v>
       </c>
       <c r="P86">
-        <v>2.527164224</v>
+        <v>2.49971856</v>
       </c>
       <c r="Q86">
-        <v>3.697164224</v>
+        <v>3.66971856</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4110321671101765</v>
+        <v>0.4340205687303203</v>
       </c>
       <c r="T86">
-        <v>4.375387250611296</v>
+        <v>4.650782378473534</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.096176371646624</v>
+        <v>2.071515473156664</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.112136985309548</v>
+        <v>0.1120282638814679</v>
       </c>
       <c r="C87">
-        <v>12.62228487449902</v>
+        <v>12.19586034374433</v>
       </c>
       <c r="D87">
-        <v>42.38228487449902</v>
+        <v>42.45186034374433</v>
       </c>
       <c r="E87">
-        <v>42.16</v>
+        <v>42.656</v>
       </c>
       <c r="F87">
-        <v>42.16</v>
+        <v>42.656</v>
       </c>
       <c r="G87">
         <v>12.4</v>
@@ -8421,28 +8421,28 @@
         <v>6.62</v>
       </c>
       <c r="M87">
-        <v>3.195728</v>
+        <v>3.2333248</v>
       </c>
       <c r="N87">
-        <v>3.424272</v>
+        <v>3.3866752</v>
       </c>
       <c r="O87">
-        <v>0.9245534400000002</v>
+        <v>0.9144023040000001</v>
       </c>
       <c r="P87">
-        <v>2.49971856</v>
+        <v>2.472272896</v>
       </c>
       <c r="Q87">
-        <v>3.66971856</v>
+        <v>3.642272896</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4340205687303203</v>
+        <v>0.4602930277247706</v>
       </c>
       <c r="T87">
-        <v>4.650782378473534</v>
+        <v>4.965519667458951</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.071515473156664</v>
+        <v>2.047428083933912</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1120282638814679</v>
+        <v>0.1119195424533877</v>
       </c>
       <c r="C88">
-        <v>12.19586034374433</v>
+        <v>11.76966462111795</v>
       </c>
       <c r="D88">
-        <v>42.45186034374433</v>
+        <v>42.52166462111795</v>
       </c>
       <c r="E88">
-        <v>42.656</v>
+        <v>43.152</v>
       </c>
       <c r="F88">
-        <v>42.656</v>
+        <v>43.152</v>
       </c>
       <c r="G88">
         <v>12.4</v>
@@ -8503,28 +8503,28 @@
         <v>6.62</v>
       </c>
       <c r="M88">
-        <v>3.2333248</v>
+        <v>3.2709216</v>
       </c>
       <c r="N88">
-        <v>3.3866752</v>
+        <v>3.3490784</v>
       </c>
       <c r="O88">
-        <v>0.9144023040000001</v>
+        <v>0.904251168</v>
       </c>
       <c r="P88">
-        <v>2.472272896</v>
+        <v>2.444827232</v>
       </c>
       <c r="Q88">
-        <v>3.642272896</v>
+        <v>3.614827232</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4602930277247706</v>
+        <v>0.4906074034875976</v>
       </c>
       <c r="T88">
-        <v>4.965519667458951</v>
+        <v>5.328678077826737</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.047428083933912</v>
+        <v>2.023894427796741</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1119195424533877</v>
+        <v>0.1118108210253075</v>
       </c>
       <c r="C89">
-        <v>11.76966462111795</v>
+        <v>11.3436988371775</v>
       </c>
       <c r="D89">
-        <v>42.52166462111795</v>
+        <v>42.5916988371775</v>
       </c>
       <c r="E89">
-        <v>43.152</v>
+        <v>43.648</v>
       </c>
       <c r="F89">
-        <v>43.152</v>
+        <v>43.648</v>
       </c>
       <c r="G89">
         <v>12.4</v>
@@ -8585,28 +8585,28 @@
         <v>6.62</v>
       </c>
       <c r="M89">
-        <v>3.2709216</v>
+        <v>3.308518400000001</v>
       </c>
       <c r="N89">
-        <v>3.3490784</v>
+        <v>3.3114816</v>
       </c>
       <c r="O89">
-        <v>0.904251168</v>
+        <v>0.894100032</v>
       </c>
       <c r="P89">
-        <v>2.444827232</v>
+        <v>2.417381568</v>
       </c>
       <c r="Q89">
-        <v>3.614827232</v>
+        <v>3.587381568</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4906074034875976</v>
+        <v>0.525974175210896</v>
       </c>
       <c r="T89">
-        <v>5.328678077826737</v>
+        <v>5.75236288992249</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.023894427796741</v>
+        <v>2.000895627480868</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1118108210253075</v>
+        <v>0.1209278395972273</v>
       </c>
       <c r="C90">
-        <v>11.3436988371775</v>
+        <v>5.679051483680396</v>
       </c>
       <c r="D90">
-        <v>42.5916988371775</v>
+        <v>37.4230514836804</v>
       </c>
       <c r="E90">
-        <v>43.648</v>
+        <v>44.14400000000001</v>
       </c>
       <c r="F90">
-        <v>43.648</v>
+        <v>44.14400000000001</v>
       </c>
       <c r="G90">
         <v>12.4</v>
@@ -8667,45 +8667,45 @@
         <v>6.62</v>
       </c>
       <c r="M90">
-        <v>3.308518400000001</v>
+        <v>3.97296</v>
       </c>
       <c r="N90">
-        <v>3.3114816</v>
+        <v>2.64704</v>
       </c>
       <c r="O90">
-        <v>0.894100032</v>
+        <v>0.7147007999999999</v>
       </c>
       <c r="P90">
-        <v>2.417381568</v>
+        <v>1.9323392</v>
       </c>
       <c r="Q90">
-        <v>3.587381568</v>
+        <v>3.102339199999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.525974175210896</v>
+        <v>0.5677712690657031</v>
       </c>
       <c r="T90">
-        <v>5.75236288992249</v>
+        <v>6.253081304217471</v>
       </c>
       <c r="U90">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V90">
         <v>0.27</v>
       </c>
       <c r="W90">
-        <v>0.055334</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.000895627480868</v>
+        <v>1.666263944263219</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1209278395972273</v>
+        <v>0.1209227781691471</v>
       </c>
       <c r="C91">
-        <v>5.679051483680396</v>
+        <v>5.185572877167743</v>
       </c>
       <c r="D91">
-        <v>37.4230514836804</v>
+        <v>37.42557287716775</v>
       </c>
       <c r="E91">
-        <v>44.14400000000001</v>
+        <v>44.64</v>
       </c>
       <c r="F91">
-        <v>44.14400000000001</v>
+        <v>44.64</v>
       </c>
       <c r="G91">
         <v>12.4</v>
@@ -8749,28 +8749,28 @@
         <v>6.62</v>
       </c>
       <c r="M91">
-        <v>3.97296</v>
+        <v>4.0176</v>
       </c>
       <c r="N91">
-        <v>2.64704</v>
+        <v>2.6024</v>
       </c>
       <c r="O91">
-        <v>0.7147007999999999</v>
+        <v>0.7026480000000002</v>
       </c>
       <c r="P91">
-        <v>1.9323392</v>
+        <v>1.899752</v>
       </c>
       <c r="Q91">
-        <v>3.102339199999999</v>
+        <v>3.069752</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5677712690657031</v>
+        <v>0.6179277816914716</v>
       </c>
       <c r="T91">
-        <v>6.253081304217471</v>
+        <v>6.853943401371446</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.666263944263219</v>
+        <v>1.647749900438073</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1209227781691471</v>
+        <v>0.120917716741067</v>
       </c>
       <c r="C92">
-        <v>5.185572877167743</v>
+        <v>4.692094610437792</v>
       </c>
       <c r="D92">
-        <v>37.42557287716775</v>
+        <v>37.4280946104378</v>
       </c>
       <c r="E92">
-        <v>44.64</v>
+        <v>45.136</v>
       </c>
       <c r="F92">
-        <v>44.64</v>
+        <v>45.136</v>
       </c>
       <c r="G92">
         <v>12.4</v>
@@ -8831,28 +8831,28 @@
         <v>6.62</v>
       </c>
       <c r="M92">
-        <v>4.0176</v>
+        <v>4.06224</v>
       </c>
       <c r="N92">
-        <v>2.6024</v>
+        <v>2.55776</v>
       </c>
       <c r="O92">
-        <v>0.7026480000000002</v>
+        <v>0.6905952000000001</v>
       </c>
       <c r="P92">
-        <v>1.899752</v>
+        <v>1.8671648</v>
       </c>
       <c r="Q92">
-        <v>3.069752</v>
+        <v>3.0371648</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6179277816914716</v>
+        <v>0.6792301860118554</v>
       </c>
       <c r="T92">
-        <v>6.853943401371446</v>
+        <v>7.588330409004085</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.647749900438073</v>
+        <v>1.629642758675017</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.120917716741067</v>
+        <v>0.1209126553129868</v>
       </c>
       <c r="C93">
-        <v>4.692094610437792</v>
+        <v>4.198616683559294</v>
       </c>
       <c r="D93">
-        <v>37.4280946104378</v>
+        <v>37.4306166835593</v>
       </c>
       <c r="E93">
-        <v>45.136</v>
+        <v>45.63200000000001</v>
       </c>
       <c r="F93">
-        <v>45.136</v>
+        <v>45.63200000000001</v>
       </c>
       <c r="G93">
         <v>12.4</v>
@@ -8913,28 +8913,28 @@
         <v>6.62</v>
       </c>
       <c r="M93">
-        <v>4.06224</v>
+        <v>4.10688</v>
       </c>
       <c r="N93">
-        <v>2.55776</v>
+        <v>2.51312</v>
       </c>
       <c r="O93">
-        <v>0.6905952000000001</v>
+        <v>0.6785424</v>
       </c>
       <c r="P93">
-        <v>1.8671648</v>
+        <v>1.8345776</v>
       </c>
       <c r="Q93">
-        <v>3.0371648</v>
+        <v>3.0045776</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6792301860118554</v>
+        <v>0.7558581914123351</v>
       </c>
       <c r="T93">
-        <v>7.588330409004085</v>
+        <v>8.506314168544883</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.629642758675017</v>
+        <v>1.611929250428549</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1209126553129868</v>
+        <v>0.1209075938849066</v>
       </c>
       <c r="C94">
-        <v>4.198616683559294</v>
+        <v>3.705139096600917</v>
       </c>
       <c r="D94">
-        <v>37.4306166835593</v>
+        <v>37.43313909660093</v>
       </c>
       <c r="E94">
-        <v>45.63200000000001</v>
+        <v>46.12800000000001</v>
       </c>
       <c r="F94">
-        <v>45.63200000000001</v>
+        <v>46.12800000000001</v>
       </c>
       <c r="G94">
         <v>12.4</v>
@@ -8995,28 +8995,28 @@
         <v>6.62</v>
       </c>
       <c r="M94">
-        <v>4.10688</v>
+        <v>4.151520000000001</v>
       </c>
       <c r="N94">
-        <v>2.51312</v>
+        <v>2.46848</v>
       </c>
       <c r="O94">
-        <v>0.6785424</v>
+        <v>0.6664895999999999</v>
       </c>
       <c r="P94">
-        <v>1.8345776</v>
+        <v>1.8019904</v>
       </c>
       <c r="Q94">
-        <v>3.0045776</v>
+        <v>2.9719904</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7558581914123351</v>
+        <v>0.8543799126415235</v>
       </c>
       <c r="T94">
-        <v>8.506314168544883</v>
+        <v>9.686579002240194</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.611929250428549</v>
+        <v>1.594596677843296</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1209075938849066</v>
+        <v>0.1209025324568264</v>
       </c>
       <c r="C95">
-        <v>3.705139096600917</v>
+        <v>3.211661849631412</v>
       </c>
       <c r="D95">
-        <v>37.43313909660093</v>
+        <v>37.43566184963142</v>
       </c>
       <c r="E95">
-        <v>46.12800000000001</v>
+        <v>46.624</v>
       </c>
       <c r="F95">
-        <v>46.12800000000001</v>
+        <v>46.624</v>
       </c>
       <c r="G95">
         <v>12.4</v>
@@ -9077,28 +9077,28 @@
         <v>6.62</v>
       </c>
       <c r="M95">
-        <v>4.151520000000001</v>
+        <v>4.19616</v>
       </c>
       <c r="N95">
-        <v>2.46848</v>
+        <v>2.42384</v>
       </c>
       <c r="O95">
-        <v>0.6664895999999999</v>
+        <v>0.6544368000000002</v>
       </c>
       <c r="P95">
-        <v>1.8019904</v>
+        <v>1.7694032</v>
       </c>
       <c r="Q95">
-        <v>2.9719904</v>
+        <v>2.9394032</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8543799126415235</v>
+        <v>0.9857422076137746</v>
       </c>
       <c r="T95">
-        <v>9.686579002240194</v>
+        <v>11.26026544716728</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.594596677843296</v>
+        <v>1.577632883398155</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1209025324568264</v>
+        <v>0.1208974710287462</v>
       </c>
       <c r="C96">
-        <v>3.211661849631412</v>
+        <v>2.718184942719503</v>
       </c>
       <c r="D96">
-        <v>37.43566184963142</v>
+        <v>37.43818494271951</v>
       </c>
       <c r="E96">
-        <v>46.624</v>
+        <v>47.12</v>
       </c>
       <c r="F96">
-        <v>46.624</v>
+        <v>47.12</v>
       </c>
       <c r="G96">
         <v>12.4</v>
@@ -9159,28 +9159,28 @@
         <v>6.62</v>
       </c>
       <c r="M96">
-        <v>4.19616</v>
+        <v>4.2408</v>
       </c>
       <c r="N96">
-        <v>2.42384</v>
+        <v>2.3792</v>
       </c>
       <c r="O96">
-        <v>0.6544368000000002</v>
+        <v>0.6423840000000001</v>
       </c>
       <c r="P96">
-        <v>1.7694032</v>
+        <v>1.736816</v>
       </c>
       <c r="Q96">
-        <v>2.9394032</v>
+        <v>2.906816</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9857422076137746</v>
+        <v>1.169649420574926</v>
       </c>
       <c r="T96">
-        <v>11.26026544716728</v>
+        <v>13.4634264700652</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.577632883398155</v>
+        <v>1.561026221467648</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1208974710287462</v>
+        <v>0.1208924096006661</v>
       </c>
       <c r="C97">
-        <v>2.718184942719503</v>
+        <v>2.224708375933965</v>
       </c>
       <c r="D97">
-        <v>37.43818494271951</v>
+        <v>37.44070837593397</v>
       </c>
       <c r="E97">
-        <v>47.12</v>
+        <v>47.61600000000001</v>
       </c>
       <c r="F97">
-        <v>47.12</v>
+        <v>47.61600000000001</v>
       </c>
       <c r="G97">
         <v>12.4</v>
@@ -9241,28 +9241,28 @@
         <v>6.62</v>
       </c>
       <c r="M97">
-        <v>4.2408</v>
+        <v>4.28544</v>
       </c>
       <c r="N97">
-        <v>2.3792</v>
+        <v>2.33456</v>
       </c>
       <c r="O97">
-        <v>0.6423840000000001</v>
+        <v>0.6303312</v>
       </c>
       <c r="P97">
-        <v>1.736816</v>
+        <v>1.7042288</v>
       </c>
       <c r="Q97">
-        <v>2.906816</v>
+        <v>2.8742288</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.169649420574926</v>
+        <v>1.445510240016654</v>
       </c>
       <c r="T97">
-        <v>13.4634264700652</v>
+        <v>16.76816800441207</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.561026221467648</v>
+        <v>1.544765531660693</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1208924096006661</v>
+        <v>0.1208873481725859</v>
       </c>
       <c r="C98">
-        <v>2.224708375933972</v>
+        <v>1.731232149343569</v>
       </c>
       <c r="D98">
-        <v>37.44070837593397</v>
+        <v>37.44323214934357</v>
       </c>
       <c r="E98">
-        <v>47.616</v>
+        <v>48.112</v>
       </c>
       <c r="F98">
-        <v>47.616</v>
+        <v>48.112</v>
       </c>
       <c r="G98">
         <v>12.4</v>
@@ -9323,28 +9323,28 @@
         <v>6.62</v>
       </c>
       <c r="M98">
-        <v>4.285439999999999</v>
+        <v>4.33008</v>
       </c>
       <c r="N98">
-        <v>2.334560000000001</v>
+        <v>2.28992</v>
       </c>
       <c r="O98">
-        <v>0.6303312000000002</v>
+        <v>0.6182784000000001</v>
       </c>
       <c r="P98">
-        <v>1.704228800000001</v>
+        <v>1.6716416</v>
       </c>
       <c r="Q98">
-        <v>2.8742288</v>
+        <v>2.8416416</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.44551024001665</v>
+        <v>1.905278272419528</v>
       </c>
       <c r="T98">
-        <v>16.76816800441203</v>
+        <v>22.2760705616568</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.544765531660693</v>
+        <v>1.528840113808521</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1208873481725859</v>
+        <v>0.1208822867445057</v>
       </c>
       <c r="C99">
-        <v>1.731232149343569</v>
+        <v>1.237756263017118</v>
       </c>
       <c r="D99">
-        <v>37.44323214934357</v>
+        <v>37.44575626301712</v>
       </c>
       <c r="E99">
-        <v>48.112</v>
+        <v>48.608</v>
       </c>
       <c r="F99">
-        <v>48.112</v>
+        <v>48.608</v>
       </c>
       <c r="G99">
         <v>12.4</v>
@@ -9405,28 +9405,28 @@
         <v>6.62</v>
       </c>
       <c r="M99">
-        <v>4.33008</v>
+        <v>4.37472</v>
       </c>
       <c r="N99">
-        <v>2.28992</v>
+        <v>2.24528</v>
       </c>
       <c r="O99">
-        <v>0.6182784000000001</v>
+        <v>0.6062256</v>
       </c>
       <c r="P99">
-        <v>1.6716416</v>
+        <v>1.6390544</v>
       </c>
       <c r="Q99">
-        <v>2.8416416</v>
+        <v>2.8090544</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.905278272419528</v>
+        <v>2.824814337225283</v>
       </c>
       <c r="T99">
-        <v>22.2760705616568</v>
+        <v>33.29187567614635</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.528840113808521</v>
+        <v>1.513239704483944</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1208822867445057</v>
+        <v>0.1667791430617992</v>
       </c>
       <c r="C100">
-        <v>1.237756263017118</v>
+        <v>-13.46434944578397</v>
       </c>
       <c r="D100">
-        <v>37.44575626301712</v>
+        <v>23.23965055421602</v>
       </c>
       <c r="E100">
-        <v>48.608</v>
+        <v>49.104</v>
       </c>
       <c r="F100">
-        <v>48.608</v>
+        <v>49.104</v>
       </c>
       <c r="G100">
         <v>12.4</v>
@@ -9487,129 +9487,47 @@
         <v>6.62</v>
       </c>
       <c r="M100">
-        <v>4.37472</v>
+        <v>7.2084672</v>
       </c>
       <c r="N100">
-        <v>2.24528</v>
+        <v>-0.5884672000000002</v>
       </c>
       <c r="O100">
-        <v>0.6062256</v>
+        <v>-0.1588861440000001</v>
       </c>
       <c r="P100">
-        <v>1.6390544</v>
+        <v>-0.4295810560000001</v>
       </c>
       <c r="Q100">
-        <v>2.8090544</v>
+        <v>0.7404189439999997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.824814337225283</v>
+        <v>5.748343338437981</v>
       </c>
       <c r="T100">
-        <v>33.29187567614635</v>
+        <v>68.31499978897864</v>
       </c>
       <c r="U100">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.27</v>
+        <v>0.2479584009205175</v>
       </c>
       <c r="W100">
-        <v>0.06569999999999999</v>
+        <v>0.110399706744868</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>1.513239704483944</v>
+        <v>0.9183644478537684</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1667791430617992</v>
-      </c>
-      <c r="C101">
-        <v>-13.46434944578397</v>
-      </c>
-      <c r="D101">
-        <v>23.23965055421602</v>
-      </c>
-      <c r="E101">
-        <v>49.104</v>
-      </c>
-      <c r="F101">
-        <v>49.104</v>
-      </c>
-      <c r="G101">
-        <v>12.4</v>
-      </c>
-      <c r="H101">
-        <v>49.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>7.79</v>
-      </c>
-      <c r="K101">
-        <v>1.17</v>
-      </c>
-      <c r="L101">
-        <v>6.62</v>
-      </c>
-      <c r="M101">
-        <v>7.2084672</v>
-      </c>
-      <c r="N101">
-        <v>-0.5884672000000002</v>
-      </c>
-      <c r="O101">
-        <v>-0.1588861440000001</v>
-      </c>
-      <c r="P101">
-        <v>-0.4295810560000001</v>
-      </c>
-      <c r="Q101">
-        <v>0.7404189439999997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.748343338437981</v>
-      </c>
-      <c r="T101">
-        <v>68.31499978897864</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.2479584009205175</v>
-      </c>
-      <c r="W101">
-        <v>0.110399706744868</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9183644478537684</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
